--- a/data/elementary.xlsx
+++ b/data/elementary.xlsx
@@ -5,11 +5,11 @@
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\새 폴더 (3)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\특수학급지도 - V3\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="17715" windowHeight="6315" tabRatio="500"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="28545" windowHeight="11325" tabRatio="500"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="elementary" sheetId="1" r:id="rId4"/>
@@ -19,339 +19,235 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="233">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="233">
+  <x:si>
+    <x:t>3명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-310-4695</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-363-1526</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 배곧4로 94-39</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 월곶해안로 69</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 능곡중앙로 22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 황고개로 567</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 목감둘레로 109</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 장곡로 70번길 12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 목감초등길 49</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 배곧 4로 44-5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 신천로 7번길 12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 목감남서로 68</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 배곧1로 28-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한국글로벌중학구/ 소래중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 계수로 203</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7096-7801</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8063-7873</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-503-1538</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8044-1261</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 해송십리로 472-30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 서울대학로 150-17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 대은로 104번길 29-10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 정왕대로 143번길 15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 옥구천동로 433-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 하중로 209번길 10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 정왕천로427번길 30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 정왕대로 53번길 14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 수인로3247번길 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 정왕대로118번길 27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 수인로 3413번길 34</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 신현로 202번길 31</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7096-7706</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-503-0560</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한여울초등학교(복합특수)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-1683</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-2204</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-364-7903</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-0802</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 군자로 539</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-2707</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-490-8204</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 은행고길 18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8063-2903</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7014-4072</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8042-0004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-0204</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-317-2701</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공립</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 주소</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 비고</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7096-6083</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7015-4404</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-0603</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-2915</x:t>
+  </x:si>
+  <x:si>
+    <x:t>성인 · 주부 · 어르신</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 포도원로 88</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-4878-2804</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-412-4300</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7014-8703</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-503-1020</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7096-6872</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-312-3600</x:t>
+  </x:si>
+  <x:si>
+    <x:t>복특 6학급/ 시간제 2학급</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-4648-5770</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7016-3005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한국글로벌중학구
+/소래중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8042-2502</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-364-3410</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8099-5900</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8042-0700</x:t>
+  </x:si>
   <x:si>
     <x:t>⊙연성초등학교 학구 중 목감동 1~2통, 3통 4반~6반은 목감중학구 및 안산시 안산중학구와 공동학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수/순회)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 해송십리로 472-30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 19명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 13명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 2학급)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 6명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 16명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(일반 : 2명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한국글로벌중학구/ 소래중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 대골안길 31</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-363-3003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 역전로 369</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8042-0700</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 10명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧누리초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧라라초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-503-1020</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-1553</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8032-6504</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8063-2903</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-2302</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥터초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시화중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>운흥초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>은계초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>승지초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>웃터골초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소래초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15/ 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>은빛초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥능곡중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소래중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시화초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>서해초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥매화중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>신천초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>월곶중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장곡초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도창초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>목감중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>월포초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24/ 12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연성초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>산현초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>목감초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>생금초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>서촌초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>송운초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장곡중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16/ 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>진영초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하중초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연성중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21/ 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3학기제</x:t>
-  </x:si>
-  <x:si>
-    <x:t>포리초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>조남초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>진말초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정왕초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 대은로 16-29</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 군자로465번길 7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 군서마을로 101</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8044-1261</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공립</x:t>
-  </x:si>
-  <x:si>
-    <x:t>⊙목감초등학교 학구 중 목감동 4통, 6통은 안산중학구와 공동학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 주소</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 비고</x:t>
-  </x:si>
-  <x:si>
-    <x:t>위도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도일초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 서울대학로 255</x:t>
-  </x:si>
-  <x:si>
-    <x:t>군자초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>냉정초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>군자중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 목감초등길 49</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 수인로2793번길 6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 배곧4로 94-39</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 배곧 4로 44-5</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 특수/순회학급수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보조인력 배치 유/무</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수/순회/일반)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 14명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(일반 : 4명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 8명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시화나래초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(일반 : 7명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 5명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>목감중학구/조남중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한국글로벌중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 21명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 3학급)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(일반 : 3명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 1학급)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 4명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(일반 : 1명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>군서미래국제학교(초)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 4학급)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 22명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(일반 : 5명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8042-2502</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 군자로 539</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-363-1526</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-494-4167</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-4648-5770</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 정왕천로427번길 30</x:t>
   </x:si>
   <x:si>
     <x:t>⊙도창초등학교 학구 중 매화동 5통, 매화동 20~22통은 시흥매화중학구와 공동학구
@@ -359,374 +255,481 @@
 ⊙도창초등학교 학구 중 과림동 1통(노무저리 제외),  과림동 2통은 광명시 광명중학군과 공동학구</x:t>
   </x:si>
   <x:si>
-    <x:t>(일반 : 10명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7014-8703</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7015-4404</x:t>
+    <x:t>소래중학구/연성중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥가온초등학교</x:t>
   </x:si>
   <x:si>
     <x:t>경기도 시흥시 나분들길 44</x:t>
   </x:si>
   <x:si>
-    <x:t>070-7096-7706</x:t>
+    <x:t>경기도 시흥시 승지로 110</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 역전로 369</x:t>
   </x:si>
   <x:si>
     <x:t>경기도 시흥시 옥터로 33</x:t>
   </x:si>
   <x:si>
+    <x:t>070-7097-2576</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 능곡군자로 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-2302</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-363-3003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 매화1로 6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-364-1700</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-1108</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-494-4167</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-1553</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8032-6504</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-434-6152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-1303</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8085-7004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7096-7772</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8099-9703</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8040-6505</x:t>
+  </x:si>
+  <x:si>
     <x:t>031-363-5904</x:t>
   </x:si>
   <x:si>
-    <x:t>070-7096-7772</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 은행고길 18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-2707</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7096-7801</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7096-6083</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-490-8204</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8085-7004</x:t>
+    <x:t>경기도 시흥시 역전로 455</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-365-8003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-500-0601</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(복합특수/시간제/일반)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 대골안길 31</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 포도원로 39</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥장현초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한국글로벌중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군서미래국제학교(초)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧누리초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥신일초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥매화초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>계수초등학교 학구 중 계수동은 부천시 소사옥길중학군과 공동학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서해초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정왕초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>검바위초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정왕중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥매화중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>목감중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하중초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>승지초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소래중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연성초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>은빛초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>산현초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>은계초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21/ 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>진말초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소래초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대야초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장곡중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>생금초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도일초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연성중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15/ 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신천초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥능곡중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>진영초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>웃터골초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수/순회)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>월곶중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>월포초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>포리초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>송운초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서촌초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도창초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>목감초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>금모래초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군서초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24/ 12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>함현초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>냉정초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>계수초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥터초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군자초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3학기제</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장곡초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>운흥초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16/ 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>조남초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시화초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시화중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군자중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥은행초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧해솔초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥월곶초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시화나래초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>목감중학구/조남중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 서울대학로 255</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 대은로103번길 24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 호현로 27번길 14</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">경기도 시흥시 은행동 663 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 죽율로 45-42</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 중심상가로 257</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 시청로80번길 5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 거북섬남로 70</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 목감둘레로 229-9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 군자로465번길 7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 군서마을로 101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 월곶중앙로 18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 수인로2793번길 6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 큰솔로 7번길 10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 대은로 16-29</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 장현능곡로 33</x:t>
+  </x:si>
+  <x:si>
+    <x:t>⊙목감초등학교 학구 중 목감동 4통, 6통은 안산중학구와 공동학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>위도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수/순회/일반)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧라온초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥능곡초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥도원초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧라라초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧한울초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 19명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 2학급)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 6명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 13명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 16명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 10명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 특수/순회학급수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보조인력 배치 유/무</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 14명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 8명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 21명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 5명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 1학급)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 3학급)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 4명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 4학급)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 22명)</x:t>
   </x:si>
   <x:si>
     <x:t>(특수 : 7명)</x:t>
   </x:si>
   <x:si>
-    <x:t>(일반 : 13명)</x:t>
+    <x:t>(특수 : 18명)</x:t>
   </x:si>
   <x:si>
     <x:t>(특수 : 2명)</x:t>
   </x:si>
   <x:si>
-    <x:t>소래중학구/연성중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-312-3600</x:t>
-  </x:si>
-  <x:si>
-    <x:t>성인 · 주부 · 어르신</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-1303</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 포도원로 39</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-365-8003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-2576</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 능곡군자로 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한여울초등학교(복합특수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>복특 6학급/ 시간제 2학급</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(복합특수/시간제/일반)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-0802</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 역전로 455</x:t>
+    <x:t>(특수 : 17명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 9명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 11명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 15명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 20명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 23명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2명</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 연락처</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 학교명</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 학교설립별</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4명</x:t>
   </x:si>
   <x:si>
     <x:t>일반학급 배치 학생 수</x:t>
   </x:si>
   <x:si>
-    <x:t>070-7097-0603</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-503-1538</x:t>
-  </x:si>
-  <x:si>
     <x:t>특수/순회학급 배치 학생 수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한국글로벌중학구
-/소래중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 계수로 203</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 옥구천동로 433-25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 정왕대로 53번길 14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 수인로 3413번길 34</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥도원초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥신일초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 17명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥매화초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥월곶초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 9명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥은행초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 18명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥장현초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥가온초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 23명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥능곡초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8042-0004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 매화1로 6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-4878-2804</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7096-6872</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-1108</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 대은로 104번길 29-10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 정왕대로 143번길 15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-317-2701</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-0204</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-310-4695</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-2915</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-2204</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 포도원로 88</x:t>
-  </x:si>
-  <x:si>
-    <x:t>함현초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대야초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 학교명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>계수초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정왕중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 연락처</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 학교설립별</x:t>
-  </x:si>
-  <x:si>
-    <x:t>검바위초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>군서초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>금모래초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>계수초등학교 학구 중 계수동은 부천시 소사옥길중학군과 공동학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 수인로3247번길 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧해솔초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 11명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 15명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧한울초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 20명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧라온초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-412-4300</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8040-6505</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8063-7873</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8099-9703</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 황고개로 567</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 시청로80번길 5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 중심상가로 257</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 배곧1로 28-25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 장현능곡로 33</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 대은로103번길 24</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 큰솔로 7번길 10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 죽율로 45-42</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 능곡중앙로 22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 신천로 7번길 12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 월곶중앙로 18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 장곡로 70번길 12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 거북섬남로 70</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 목감둘레로 229-9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 월곶해안로 69</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 호현로 27번길 14</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">경기도 시흥시 은행동 663 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 목감남서로 68</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 목감둘레로 109</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 정왕대로118번길 27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 서울대학로 150-17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-1683</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-434-6152</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-500-0601</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7016-3005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7014-4072</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-364-1700</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-364-7903</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-364-3410</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-503-0560</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 승지로 110</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8099-5900</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 신현로 202번길 31</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 하중로 209번길 10</x:t>
   </x:si>
 </x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:numFmts count="1">
+    <x:numFmt numFmtId="164" formatCode="&quot; &quot;?&quot;명&quot;"/>
+  </x:numFmts>
   <x:fonts count="6">
     <x:font>
       <x:name val="맑은 고딕"/>
@@ -783,13 +786,16 @@
       </x:bottom>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="1">
+  <x:cellStyleXfs count="2">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="3">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+  <x:cellXfs count="4">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -798,8 +804,11 @@
     <x:xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
   </x:cellXfs>
-  <x:cellStyles count="1">
+  <x:cellStyles count="2">
     <x:cellStyle name="표준" xfId="0" builtinId="0" iLevel="0"/>
   </x:cellStyles>
   <x:dxfs/>
@@ -1122,72 +1131,77 @@
   <x:sheetPr codeName="Sheet1"/>
   <x:dimension ref="A1:L53"/>
   <x:sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.39999999999999857891"/>
+  <x:cols>
+    <x:col min="6" max="6" width="27.62890625" customWidth="1"/>
+    <x:col min="7" max="7" width="24.55078125" bestFit="1" customWidth="1"/>
+    <x:col min="8" max="8" width="19.9921875" bestFit="1" customWidth="1"/>
+  </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:12">
       <x:c r="A1" t="s">
-        <x:v>178</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="B1" t="s">
-        <x:v>182</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="C1" t="s">
-        <x:v>72</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D1" t="s">
-        <x:v>71</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E1" t="s">
-        <x:v>181</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="F1" t="s">
-        <x:v>84</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="G1" t="s">
-        <x:v>145</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="H1" t="s">
-        <x:v>142</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="I1" t="s">
-        <x:v>85</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="J1" t="s">
-        <x:v>73</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K1" t="s">
-        <x:v>74</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="L1" t="s">
-        <x:v>68</x:v>
+        <x:v>190</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:12" ht="65.5">
       <x:c r="A2" t="s">
-        <x:v>183</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B2" t="s">
-        <x:v>69</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D2" t="s">
-        <x:v>187</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E2" t="s">
-        <x:v>144</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F2" t="s">
-        <x:v>96</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="G2" t="s">
-        <x:v>95</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="H2" t="s">
-        <x:v>97</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I2" t="s">
-        <x:v>67</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="K2">
         <x:v>37.432746760000001</x:v>
@@ -1198,34 +1212,34 @@
     </x:row>
     <x:row r="3" spans="1:12">
       <x:c r="A3" t="s">
-        <x:v>179</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="B3" t="s">
-        <x:v>69</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C3" t="s">
-        <x:v>94</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D3" t="s">
-        <x:v>147</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E3" t="s">
-        <x:v>66</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F3" t="s">
-        <x:v>98</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="G3" t="s">
-        <x:v>99</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H3" t="s">
-        <x:v>100</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="I3" t="s">
-        <x:v>188</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J3" t="s">
-        <x:v>186</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="K3">
         <x:v>37.453471950000001</x:v>
@@ -1236,31 +1250,31 @@
     </x:row>
     <x:row r="4" spans="1:12">
       <x:c r="A4" t="s">
-        <x:v>101</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B4" t="s">
-        <x:v>69</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C4" t="s">
-        <x:v>188</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D4" t="s">
-        <x:v>65</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="E4" t="s">
-        <x:v>107</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F4" t="s">
-        <x:v>188</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G4" t="s">
-        <x:v>188</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H4" t="s">
-        <x:v>97</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I4" t="s">
-        <x:v>188</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="K4">
         <x:v>37.34626506</x:v>
@@ -1271,31 +1285,31 @@
     </x:row>
     <x:row r="5" spans="1:12">
       <x:c r="A5" t="s">
-        <x:v>184</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="B5" t="s">
-        <x:v>69</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C5" t="s">
-        <x:v>180</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D5" t="s">
-        <x:v>110</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E5" t="s">
-        <x:v>105</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F5" t="s">
-        <x:v>96</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="G5" t="s">
-        <x:v>103</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="H5" t="s">
-        <x:v>104</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="I5" t="s">
-        <x:v>67</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="K5">
         <x:v>37.347420020000001</x:v>
@@ -1306,31 +1320,31 @@
     </x:row>
     <x:row r="6" spans="1:12">
       <x:c r="A6" t="s">
-        <x:v>77</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="B6" t="s">
-        <x:v>69</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C6" t="s">
-        <x:v>79</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="D6" t="s">
-        <x:v>106</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E6" t="s">
-        <x:v>109</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F6" t="s">
-        <x:v>102</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="G6" t="s">
-        <x:v>95</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="H6" t="s">
-        <x:v>100</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="I6" t="s">
-        <x:v>67</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="K6">
         <x:v>37.343899370000003</x:v>
@@ -1341,31 +1355,31 @@
     </x:row>
     <x:row r="7" spans="1:12" ht="65.5">
       <x:c r="A7" t="s">
-        <x:v>185</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="B7" t="s">
-        <x:v>69</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D7" t="s">
-        <x:v>63</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="E7" t="s">
-        <x:v>143</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F7" t="s">
-        <x:v>5</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="G7" t="s">
-        <x:v>4</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="H7" t="s">
-        <x:v>104</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="I7" t="s">
-        <x:v>67</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="K7">
         <x:v>37.441589</x:v>
@@ -1376,31 +1390,31 @@
     </x:row>
     <x:row r="8" spans="1:12">
       <x:c r="A8" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="B8" t="s">
-        <x:v>69</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C8" t="s">
-        <x:v>180</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D8" t="s">
-        <x:v>12</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E8" t="s">
-        <x:v>13</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F8" t="s">
-        <x:v>96</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="G8" t="s">
-        <x:v>3</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="H8" t="s">
-        <x:v>97</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I8" t="s">
-        <x:v>67</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="K8">
         <x:v>37.357741859999997</x:v>
@@ -1411,31 +1425,31 @@
     </x:row>
     <x:row r="9" spans="1:12">
       <x:c r="A9" t="s">
-        <x:v>177</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B9" t="s">
-        <x:v>69</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C9" t="s">
-        <x:v>9</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D9" t="s">
-        <x:v>10</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E9" t="s">
-        <x:v>11</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="F9" t="s">
-        <x:v>96</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="G9" t="s">
-        <x:v>7</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="H9" t="s">
-        <x:v>8</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="I9" t="s">
-        <x:v>188</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="K9">
         <x:v>37.446825369999999</x:v>
@@ -1446,19 +1460,19 @@
     </x:row>
     <x:row r="10" spans="1:12">
       <x:c r="A10" t="s">
-        <x:v>75</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B10" t="s">
-        <x:v>69</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C10" t="s">
-        <x:v>79</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="D10" t="s">
-        <x:v>64</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="E10" t="s">
-        <x:v>108</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F10" s="2">
         <x:v>46054</x:v>
@@ -1467,13 +1481,13 @@
         <x:v>46268</x:v>
       </x:c>
       <x:c r="H10" t="s">
-        <x:v>188</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I10" t="s">
-        <x:v>188</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J10" t="s">
-        <x:v>1</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="K10">
         <x:v>37.349119160000001</x:v>
@@ -1484,22 +1498,22 @@
     </x:row>
     <x:row r="11" spans="1:12" ht="409.5">
       <x:c r="A11" t="s">
-        <x:v>40</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B11" t="s">
-        <x:v>69</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D11" t="s">
-        <x:v>81</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="E11" t="s">
-        <x:v>21</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F11" t="s">
-        <x:v>188</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G11">
         <x:v>0</x:v>
@@ -1508,10 +1522,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I11" t="s">
-        <x:v>188</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J11" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="K11">
         <x:v>37.406893609999997</x:v>
@@ -1522,34 +1536,34 @@
     </x:row>
     <x:row r="12" spans="1:12">
       <x:c r="A12" t="s">
-        <x:v>48</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="B12" t="s">
-        <x:v>69</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C12" t="s">
-        <x:v>41</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D12" t="s">
-        <x:v>80</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E12" t="s">
-        <x:v>18</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="F12" t="s">
-        <x:v>5</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="G12" t="s">
-        <x:v>14</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="H12" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="I12" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="J12" t="s">
         <x:v>188</x:v>
-      </x:c>
-      <x:c r="I12" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="J12" t="s">
-        <x:v>70</x:v>
       </x:c>
       <x:c r="K12">
         <x:v>37.386862639999997</x:v>
@@ -1560,31 +1574,31 @@
     </x:row>
     <x:row r="13" spans="1:12">
       <x:c r="A13" t="s">
-        <x:v>15</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B13" t="s">
-        <x:v>69</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C13" t="s">
-        <x:v>42</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D13" t="s">
-        <x:v>2</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E13" t="s">
-        <x:v>20</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F13" t="s">
-        <x:v>102</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="G13" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="H13" t="s">
-        <x:v>104</x:v>
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="H13" s="3" t="s">
+        <x:v>224</x:v>
       </x:c>
       <x:c r="I13" t="s">
-        <x:v>67</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="K13">
         <x:v>37.382653580000003</x:v>
@@ -1595,31 +1609,31 @@
     </x:row>
     <x:row r="14" spans="1:12">
       <x:c r="A14" t="s">
-        <x:v>16</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="B14" t="s">
-        <x:v>69</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C14" t="s">
-        <x:v>42</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D14" t="s">
-        <x:v>76</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="E14" t="s">
-        <x:v>17</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F14" t="s">
-        <x:v>98</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="G14" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H14" t="s">
-        <x:v>8</x:v>
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="H14" s="3" t="s">
+        <x:v>226</x:v>
       </x:c>
       <x:c r="I14" t="s">
-        <x:v>188</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="K14">
         <x:v>37.369258219999999</x:v>
@@ -1630,31 +1644,31 @@
     </x:row>
     <x:row r="15" spans="1:12">
       <x:c r="A15" t="s">
-        <x:v>194</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="B15" t="s">
-        <x:v>69</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C15" t="s">
-        <x:v>42</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D15" t="s">
-        <x:v>82</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E15" t="s">
-        <x:v>19</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F15" t="s">
-        <x:v>96</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="G15" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="H15" t="s">
-        <x:v>8</x:v>
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="H15" s="3" t="s">
+        <x:v>226</x:v>
       </x:c>
       <x:c r="I15" t="s">
-        <x:v>67</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="K15">
         <x:v>37.372575730000001</x:v>
@@ -1665,31 +1679,31 @@
     </x:row>
     <x:row r="16" spans="1:12">
       <x:c r="A16" t="s">
-        <x:v>22</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="B16" t="s">
-        <x:v>69</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C16" t="s">
-        <x:v>42</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D16" t="s">
-        <x:v>83</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E16" t="s">
-        <x:v>198</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="F16" t="s">
-        <x:v>5</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="G16" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="H16" t="s">
-        <x:v>104</x:v>
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="H16" s="3" t="s">
+        <x:v>224</x:v>
       </x:c>
       <x:c r="I16" t="s">
-        <x:v>67</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="K16">
         <x:v>37.376015750000001</x:v>
@@ -1700,31 +1714,31 @@
     </x:row>
     <x:row r="17" spans="1:12">
       <x:c r="A17" t="s">
-        <x:v>192</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="B17" t="s">
-        <x:v>69</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C17" t="s">
-        <x:v>42</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D17" t="s">
-        <x:v>202</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E17" t="s">
-        <x:v>195</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F17" t="s">
-        <x:v>96</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="G17" t="s">
-        <x:v>3</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="H17" t="s">
-        <x:v>188</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I17" t="s">
-        <x:v>67</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="K17">
         <x:v>37.360501769999999</x:v>
@@ -1735,31 +1749,31 @@
     </x:row>
     <x:row r="18" spans="1:12">
       <x:c r="A18" t="s">
-        <x:v>189</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="B18" t="s">
-        <x:v>69</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C18" t="s">
-        <x:v>42</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D18" t="s">
-        <x:v>219</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E18" t="s">
-        <x:v>197</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F18" t="s">
-        <x:v>5</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="G18" t="s">
-        <x:v>190</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="H18" t="s">
-        <x:v>104</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="I18" t="s">
-        <x:v>67</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="K18">
         <x:v>37.360535210000002</x:v>
@@ -1770,31 +1784,31 @@
     </x:row>
     <x:row r="19" spans="1:12">
       <x:c r="A19" t="s">
-        <x:v>47</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B19" t="s">
-        <x:v>69</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C19" t="s">
-        <x:v>93</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="D19" t="s">
-        <x:v>216</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E19" t="s">
-        <x:v>196</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F19" t="s">
-        <x:v>5</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="G19" t="s">
-        <x:v>4</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="H19" t="s">
-        <x:v>188</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I19" t="s">
-        <x:v>67</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="K19">
         <x:v>37.37494805</x:v>
@@ -1805,31 +1819,31 @@
     </x:row>
     <x:row r="20" spans="1:12">
       <x:c r="A20" t="s">
-        <x:v>49</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B20" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C20" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="D20" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="E20" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="C20" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="D20" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="E20" t="s">
-        <x:v>223</x:v>
-      </x:c>
       <x:c r="F20" t="s">
-        <x:v>98</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="G20" t="s">
-        <x:v>92</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H20" t="s">
-        <x:v>104</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="I20" t="s">
-        <x:v>188</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="K20">
         <x:v>37.350397829999999</x:v>
@@ -1840,31 +1854,31 @@
     </x:row>
     <x:row r="21" spans="1:12">
       <x:c r="A21" t="s">
-        <x:v>50</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B21" t="s">
-        <x:v>69</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C21" t="s">
-        <x:v>180</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D21" t="s">
-        <x:v>218</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E21" t="s">
-        <x:v>224</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F21" t="s">
-        <x:v>5</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="G21" t="s">
-        <x:v>4</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="H21" t="s">
-        <x:v>100</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="I21" t="s">
-        <x:v>67</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="K21">
         <x:v>37.349460039999997</x:v>
@@ -1875,34 +1889,34 @@
     </x:row>
     <x:row r="22" spans="1:12">
       <x:c r="A22" t="s">
-        <x:v>35</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B22" t="s">
-        <x:v>69</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C22" t="s">
-        <x:v>180</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D22" t="s">
-        <x:v>149</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E22" t="s">
-        <x:v>221</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F22" s="2">
         <x:v>46082</x:v>
       </x:c>
       <x:c r="G22" t="s">
-        <x:v>53</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="H22" t="s">
-        <x:v>100</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="I22" t="s">
-        <x:v>67</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="J22" t="s">
-        <x:v>86</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="K22">
         <x:v>37.356151019999999</x:v>
@@ -1913,31 +1927,31 @@
     </x:row>
     <x:row r="23" spans="1:12">
       <x:c r="A23" t="s">
-        <x:v>29</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B23" t="s">
-        <x:v>69</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C23" t="s">
-        <x:v>33</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D23" t="s">
-        <x:v>214</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="E23" t="s">
-        <x:v>220</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F23" t="s">
-        <x:v>5</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="G23" t="s">
-        <x:v>89</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="H23" t="s">
-        <x:v>100</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="I23" t="s">
-        <x:v>67</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="K23">
         <x:v>37.443772459999998</x:v>
@@ -1948,31 +1962,31 @@
     </x:row>
     <x:row r="24" spans="1:12">
       <x:c r="A24" t="s">
-        <x:v>51</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B24" t="s">
-        <x:v>69</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C24" t="s">
-        <x:v>180</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D24" t="s">
-        <x:v>148</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E24" t="s">
-        <x:v>222</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="F24" t="s">
-        <x:v>5</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="G24" t="s">
-        <x:v>87</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="H24" t="s">
-        <x:v>88</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="I24" t="s">
-        <x:v>67</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="K24">
         <x:v>35.228763190000002</x:v>
@@ -1983,31 +1997,31 @@
     </x:row>
     <x:row r="25" spans="1:12">
       <x:c r="A25" t="s">
-        <x:v>27</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B25" t="s">
-        <x:v>69</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C25" t="s">
-        <x:v>32</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="D25" t="s">
-        <x:v>229</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E25" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="F25" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="G25" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="H25" t="s">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="F25" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G25" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="H25" t="s">
-        <x:v>88</x:v>
-      </x:c>
       <x:c r="I25" t="s">
-        <x:v>67</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="K25">
         <x:v>37.372313550000001</x:v>
@@ -2018,31 +2032,31 @@
     </x:row>
     <x:row r="26" spans="1:12">
       <x:c r="A26" t="s">
-        <x:v>90</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="B26" t="s">
-        <x:v>69</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C26" t="s">
-        <x:v>24</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="D26" t="s">
-        <x:v>211</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="E26" t="s">
-        <x:v>227</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F26" t="s">
-        <x:v>5</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="G26" t="s">
-        <x:v>87</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="H26" t="s">
-        <x:v>91</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="I26" t="s">
-        <x:v>67</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="K26">
         <x:v>37.320716019999999</x:v>
@@ -2053,31 +2067,31 @@
     </x:row>
     <x:row r="27" spans="1:12">
       <x:c r="A27" t="s">
-        <x:v>34</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="B27" t="s">
-        <x:v>69</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C27" t="s">
-        <x:v>180</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D27" t="s">
-        <x:v>205</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="E27" t="s">
-        <x:v>228</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F27" t="s">
-        <x:v>5</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="G27" t="s">
-        <x:v>191</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="H27" t="s">
-        <x:v>8</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="I27" t="s">
-        <x:v>67</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="K27">
         <x:v>37.339255610000002</x:v>
@@ -2088,31 +2102,31 @@
     </x:row>
     <x:row r="28" spans="1:12">
       <x:c r="A28" t="s">
-        <x:v>160</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B28" t="s">
-        <x:v>69</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C28" t="s">
-        <x:v>52</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D28" t="s">
-        <x:v>203</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="E28" t="s">
-        <x:v>225</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="F28" t="s">
-        <x:v>96</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="G28" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="H28" t="s">
-        <x:v>88</x:v>
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="H28" s="3" t="s">
+        <x:v>230</x:v>
       </x:c>
       <x:c r="I28" t="s">
-        <x:v>67</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="K28">
         <x:v>37.37378717</x:v>
@@ -2123,31 +2137,31 @@
     </x:row>
     <x:row r="29" spans="1:12">
       <x:c r="A29" t="s">
-        <x:v>162</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="B29" t="s">
-        <x:v>69</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C29" t="s">
-        <x:v>32</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="D29" t="s">
-        <x:v>207</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E29" t="s">
-        <x:v>166</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F29" t="s">
-        <x:v>5</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="G29" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="H29" t="s">
-        <x:v>100</x:v>
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="H29" s="3" t="s">
+        <x:v>113</x:v>
       </x:c>
       <x:c r="I29" t="s">
-        <x:v>188</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="K29">
         <x:v>37.365372309999998</x:v>
@@ -2158,31 +2172,31 @@
     </x:row>
     <x:row r="30" spans="1:12">
       <x:c r="A30" t="s">
-        <x:v>151</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="B30" t="s">
-        <x:v>69</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C30" t="s">
-        <x:v>33</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D30" t="s">
-        <x:v>150</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E30" t="s">
-        <x:v>167</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F30" t="s">
-        <x:v>98</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="G30" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="H30" t="s">
-        <x:v>100</x:v>
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="H30" s="3" t="s">
+        <x:v>113</x:v>
       </x:c>
       <x:c r="I30" t="s">
-        <x:v>188</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="K30">
         <x:v>37.440093009999998</x:v>
@@ -2193,31 +2207,31 @@
     </x:row>
     <x:row r="31" spans="1:12">
       <x:c r="A31" t="s">
-        <x:v>154</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B31" t="s">
-        <x:v>69</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C31" t="s">
-        <x:v>36</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D31" t="s">
-        <x:v>164</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E31" t="s">
-        <x:v>163</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F31" t="s">
-        <x:v>96</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="G31" t="s">
-        <x:v>153</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="H31" t="s">
-        <x:v>188</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I31" t="s">
-        <x:v>188</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="K31">
         <x:v>37.416300909999997</x:v>
@@ -2228,31 +2242,31 @@
     </x:row>
     <x:row r="32" spans="1:12">
       <x:c r="A32" t="s">
-        <x:v>152</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B32" t="s">
-        <x:v>69</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C32" t="s">
-        <x:v>33</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D32" t="s">
-        <x:v>208</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E32" t="s">
-        <x:v>165</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F32" t="s">
-        <x:v>5</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="G32" t="s">
-        <x:v>89</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="H32" t="s">
-        <x:v>8</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="I32" t="s">
-        <x:v>188</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="K32">
         <x:v>37.433075209999998</x:v>
@@ -2263,31 +2277,31 @@
     </x:row>
     <x:row r="33" spans="1:12">
       <x:c r="A33" t="s">
-        <x:v>155</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="B33" t="s">
-        <x:v>69</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C33" t="s">
-        <x:v>38</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D33" t="s">
-        <x:v>213</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E33" t="s">
-        <x:v>226</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F33" t="s">
-        <x:v>5</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="G33" t="s">
-        <x:v>156</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="H33" t="s">
-        <x:v>88</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="I33" t="s">
-        <x:v>67</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="K33">
         <x:v>37.391718959999999</x:v>
@@ -2298,31 +2312,31 @@
     </x:row>
     <x:row r="34" spans="1:12" ht="65.5">
       <x:c r="A34" t="s">
-        <x:v>157</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="B34" t="s">
-        <x:v>69</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D34" t="s">
-        <x:v>168</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E34" t="s">
-        <x:v>171</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F34" t="s">
-        <x:v>96</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="G34" t="s">
-        <x:v>158</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="H34" t="s">
-        <x:v>8</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="I34" t="s">
-        <x:v>188</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="K34">
         <x:v>37.442591470000004</x:v>
@@ -2333,31 +2347,31 @@
     </x:row>
     <x:row r="35" spans="1:12">
       <x:c r="A35" t="s">
-        <x:v>159</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B35" t="s">
-        <x:v>69</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C35" t="s">
-        <x:v>52</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D35" t="s">
-        <x:v>200</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="E35" t="s">
-        <x:v>172</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F35" t="s">
-        <x:v>5</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="G35" t="s">
-        <x:v>156</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="H35" t="s">
-        <x:v>88</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="I35" t="s">
-        <x:v>67</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="K35">
         <x:v>37.381790879999997</x:v>
@@ -2368,31 +2382,31 @@
     </x:row>
     <x:row r="36" spans="1:12">
       <x:c r="A36" t="s">
-        <x:v>43</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B36" t="s">
-        <x:v>69</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C36" t="s">
-        <x:v>180</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D36" t="s">
-        <x:v>169</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E36" t="s">
-        <x:v>173</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F36" t="s">
-        <x:v>96</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="G36" t="s">
-        <x:v>158</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="H36" t="s">
-        <x:v>97</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I36" t="s">
-        <x:v>67</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="K36">
         <x:v>33.479625749999997</x:v>
@@ -2403,31 +2417,31 @@
     </x:row>
     <x:row r="37" spans="1:12">
       <x:c r="A37" t="s">
-        <x:v>37</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B37" t="s">
-        <x:v>69</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C37" t="s">
-        <x:v>33</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D37" t="s">
-        <x:v>175</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E37" t="s">
-        <x:v>174</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F37" t="s">
-        <x:v>5</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="G37" t="s">
-        <x:v>190</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="H37" t="s">
-        <x:v>188</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I37" t="s">
-        <x:v>188</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="K37">
         <x:v>37.43524335</x:v>
@@ -2438,34 +2452,34 @@
     </x:row>
     <x:row r="38" spans="1:12">
       <x:c r="A38" t="s">
-        <x:v>46</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B38" t="s">
-        <x:v>69</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C38" t="s">
-        <x:v>41</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D38" t="s">
-        <x:v>115</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E38" t="s">
-        <x:v>113</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F38" t="s">
-        <x:v>5</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="G38" t="s">
-        <x:v>89</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="H38" t="s">
-        <x:v>188</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I38" t="s">
-        <x:v>67</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="J38" t="s">
-        <x:v>0</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="K38">
         <x:v>37.387563890000003</x:v>
@@ -2476,31 +2490,31 @@
     </x:row>
     <x:row r="39" spans="1:12">
       <x:c r="A39" t="s">
-        <x:v>23</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="B39" t="s">
-        <x:v>69</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C39" t="s">
-        <x:v>180</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D39" t="s">
-        <x:v>117</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E39" t="s">
-        <x:v>114</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F39" t="s">
-        <x:v>5</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="G39" t="s">
-        <x:v>191</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="H39" t="s">
-        <x:v>188</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I39" t="s">
-        <x:v>67</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="K39">
         <x:v>37.345110460000001</x:v>
@@ -2511,31 +2525,31 @@
     </x:row>
     <x:row r="40" spans="1:12">
       <x:c r="A40" t="s">
-        <x:v>25</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="B40" t="s">
-        <x:v>69</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C40" t="s">
-        <x:v>93</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="D40" t="s">
-        <x:v>217</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E40" t="s">
-        <x:v>118</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="F40" t="s">
-        <x:v>5</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="G40" t="s">
-        <x:v>87</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="H40" t="s">
-        <x:v>112</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="I40" t="s">
-        <x:v>67</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="K40">
         <x:v>37.372765039999997</x:v>
@@ -2546,31 +2560,31 @@
     </x:row>
     <x:row r="41" spans="1:12" ht="65.5">
       <x:c r="A41" t="s">
-        <x:v>28</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B41" t="s">
-        <x:v>69</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D41" t="s">
-        <x:v>120</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E41" t="s">
-        <x:v>116</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F41" t="s">
-        <x:v>5</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="G41" t="s">
-        <x:v>156</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="H41" t="s">
-        <x:v>8</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="I41" t="s">
-        <x:v>67</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="K41">
         <x:v>37.439720010000002</x:v>
@@ -2581,31 +2595,31 @@
     </x:row>
     <x:row r="42" spans="1:12">
       <x:c r="A42" t="s">
-        <x:v>44</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B42" t="s">
-        <x:v>69</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C42" t="s">
-        <x:v>38</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D42" t="s">
-        <x:v>209</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="E42" t="s">
-        <x:v>121</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F42" t="s">
-        <x:v>5</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="G42" t="s">
-        <x:v>156</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="H42" t="s">
-        <x:v>100</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="I42" t="s">
-        <x:v>67</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="K42">
         <x:v>37.387488849999997</x:v>
@@ -2616,34 +2630,34 @@
     </x:row>
     <x:row r="43" spans="1:12" ht="65.5">
       <x:c r="A43" t="s">
-        <x:v>26</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B43" t="s">
-        <x:v>69</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D43" t="s">
-        <x:v>204</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="E43" t="s">
-        <x:v>119</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="F43" s="2">
         <x:v>46082</x:v>
       </x:c>
       <x:c r="G43" t="s">
-        <x:v>30</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="H43" t="s">
-        <x:v>97</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I43" t="s">
-        <x:v>67</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="J43" t="s">
-        <x:v>86</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="K43">
         <x:v>37.44773309</x:v>
@@ -2654,31 +2668,31 @@
     </x:row>
     <x:row r="44" spans="1:12" ht="65.5">
       <x:c r="A44" t="s">
-        <x:v>31</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B44" t="s">
-        <x:v>69</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D44" t="s">
-        <x:v>215</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="E44" t="s">
-        <x:v>125</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="F44" t="s">
-        <x:v>96</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="G44" t="s">
-        <x:v>95</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="H44" t="s">
-        <x:v>97</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I44" t="s">
-        <x:v>67</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="K44">
         <x:v>37.434280770000001</x:v>
@@ -2689,31 +2703,31 @@
     </x:row>
     <x:row r="45" spans="1:12">
       <x:c r="A45" t="s">
-        <x:v>39</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="B45" t="s">
-        <x:v>69</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C45" t="s">
-        <x:v>52</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D45" t="s">
-        <x:v>210</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E45" t="s">
-        <x:v>123</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F45" t="s">
-        <x:v>96</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="G45" t="s">
-        <x:v>87</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="H45" t="s">
-        <x:v>100</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="I45" t="s">
-        <x:v>67</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="K45">
         <x:v>37.381523569999999</x:v>
@@ -2724,34 +2738,34 @@
     </x:row>
     <x:row r="46" spans="1:12">
       <x:c r="A46" t="s">
-        <x:v>62</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B46" t="s">
-        <x:v>69</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C46" t="s">
-        <x:v>180</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D46" t="s">
-        <x:v>201</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="E46" t="s">
-        <x:v>122</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F46" s="2">
         <x:v>46082</x:v>
       </x:c>
       <x:c r="G46" t="s">
-        <x:v>57</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="H46" t="s">
-        <x:v>97</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I46" t="s">
-        <x:v>67</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="J46" t="s">
-        <x:v>86</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="K46">
         <x:v>37.341022029999998</x:v>
@@ -2762,31 +2776,31 @@
     </x:row>
     <x:row r="47" spans="1:12">
       <x:c r="A47" t="s">
-        <x:v>60</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="B47" t="s">
-        <x:v>69</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C47" t="s">
-        <x:v>93</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="D47" t="s">
-        <x:v>212</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="E47" t="s">
-        <x:v>124</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F47" t="s">
-        <x:v>5</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="G47" t="s">
-        <x:v>87</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="H47" t="s">
-        <x:v>8</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="I47" t="s">
-        <x:v>67</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="K47">
         <x:v>37.378656040000003</x:v>
@@ -2797,31 +2811,31 @@
     </x:row>
     <x:row r="48" spans="1:12">
       <x:c r="A48" t="s">
-        <x:v>61</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B48" t="s">
-        <x:v>69</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C48" t="s">
-        <x:v>52</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D48" t="s">
-        <x:v>199</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E48" t="s">
-        <x:v>170</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F48" t="s">
-        <x:v>96</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="G48" t="s">
-        <x:v>193</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="H48" t="s">
-        <x:v>127</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="I48" t="s">
-        <x:v>67</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="K48">
         <x:v>37.38076332</x:v>
@@ -2832,34 +2846,34 @@
     </x:row>
     <x:row r="49" spans="1:12">
       <x:c r="A49" t="s">
-        <x:v>54</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B49" t="s">
-        <x:v>58</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="C49" t="s">
-        <x:v>188</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D49" t="s">
-        <x:v>133</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E49" t="s">
-        <x:v>130</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F49" t="s">
-        <x:v>188</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G49" t="s">
-        <x:v>188</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H49" t="s">
-        <x:v>188</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I49" t="s">
-        <x:v>188</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J49" t="s">
-        <x:v>131</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K49">
         <x:v>37.436062530000001</x:v>
@@ -2870,31 +2884,31 @@
     </x:row>
     <x:row r="50" spans="1:12">
       <x:c r="A50" t="s">
-        <x:v>59</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B50" t="s">
-        <x:v>69</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C50" t="s">
-        <x:v>129</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D50" t="s">
-        <x:v>231</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E50" t="s">
-        <x:v>135</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="F50" t="s">
-        <x:v>98</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="G50" t="s">
-        <x:v>128</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="H50" t="s">
-        <x:v>188</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I50" t="s">
-        <x:v>188</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="K50">
         <x:v>37.405642800000003</x:v>
@@ -2905,31 +2919,31 @@
     </x:row>
     <x:row r="51" spans="1:12">
       <x:c r="A51" t="s">
-        <x:v>55</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B51" t="s">
-        <x:v>69</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C51" t="s">
-        <x:v>56</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="D51" t="s">
-        <x:v>232</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E51" t="s">
-        <x:v>132</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="F51" t="s">
-        <x:v>96</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="G51" t="s">
-        <x:v>191</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="H51" t="s">
-        <x:v>188</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I51" t="s">
-        <x:v>67</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="K51">
         <x:v>37.393327390000003</x:v>
@@ -2940,34 +2954,34 @@
     </x:row>
     <x:row r="52" spans="1:12">
       <x:c r="A52" t="s">
-        <x:v>137</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B52" t="s">
-        <x:v>69</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C52" t="s">
-        <x:v>52</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D52" t="s">
-        <x:v>136</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E52" t="s">
-        <x:v>134</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="F52" t="s">
-        <x:v>138</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="G52" t="s">
-        <x:v>45</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="H52" t="s">
-        <x:v>8</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="I52" t="s">
-        <x:v>67</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="J52" t="s">
-        <x:v>139</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="K52">
         <x:v>37.36561434</x:v>
@@ -2978,31 +2992,31 @@
     </x:row>
     <x:row r="53" spans="1:12">
       <x:c r="A53" t="s">
-        <x:v>176</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="B53" t="s">
-        <x:v>69</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C53" t="s">
-        <x:v>180</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D53" t="s">
-        <x:v>141</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E53" t="s">
-        <x:v>140</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F53" t="s">
-        <x:v>98</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="G53" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="H53">
-        <x:v>1</x:v>
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="H53" t="s">
+        <x:v>113</x:v>
       </x:c>
       <x:c r="I53" t="s">
-        <x:v>188</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="K53">
         <x:v>37.365442260000002</x:v>
@@ -3012,7 +3026,7 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51180553436279296875" footer="0.51180553436279296875"/>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51166665554046630859" footer="0.51166665554046630859"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1"/>
 </x:worksheet>

--- a/data/elementary.xlsx
+++ b/data/elementary.xlsx
@@ -5,7 +5,7 @@
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\특수학급지도 - V3\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\특수학급지도 - V3 final + 꿈이든 + 번역기\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
@@ -21,184 +21,43 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="233">
   <x:si>
-    <x:t>3명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-310-4695</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-363-1526</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 배곧4로 94-39</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 월곶해안로 69</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 능곡중앙로 22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 황고개로 567</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 목감둘레로 109</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 장곡로 70번길 12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 목감초등길 49</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 배곧 4로 44-5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 신천로 7번길 12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 목감남서로 68</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 배곧1로 28-25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한국글로벌중학구/ 소래중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 계수로 203</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7096-7801</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8063-7873</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-503-1538</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8044-1261</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 해송십리로 472-30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 서울대학로 150-17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 대은로 104번길 29-10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 정왕대로 143번길 15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 옥구천동로 433-25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 하중로 209번길 10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 정왕천로427번길 30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 정왕대로 53번길 14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 수인로3247번길 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 정왕대로118번길 27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 수인로 3413번길 34</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 신현로 202번길 31</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7096-7706</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-503-0560</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한여울초등학교(복합특수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-1683</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-2204</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-364-7903</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-0802</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 군자로 539</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-2707</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-490-8204</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 은행고길 18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8063-2903</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7014-4072</x:t>
+    <x:t>⊙연성초등학교 학구 중 목감동 1~2통, 3통 4반~6반은 목감중학구 및 안산시 안산중학구와 공동학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수/순회/일반)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥능곡초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧라온초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥도원초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧라라초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧한울초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소래중학구/연성중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥가온초등학교</x:t>
   </x:si>
   <x:si>
     <x:t>031-8042-0004</x:t>
   </x:si>
   <x:si>
+    <x:t>031-317-2701</x:t>
+  </x:si>
+  <x:si>
     <x:t>070-7097-0204</x:t>
   </x:si>
   <x:si>
-    <x:t>031-317-2701</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공립</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 주소</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 비고</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7096-6083</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7015-4404</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-0603</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-2915</x:t>
-  </x:si>
-  <x:si>
-    <x:t>성인 · 주부 · 어르신</x:t>
+    <x:t>070-7014-8703</x:t>
   </x:si>
   <x:si>
     <x:t>경기도 시흥시 포도원로 88</x:t>
@@ -210,44 +69,17 @@
     <x:t>031-412-4300</x:t>
   </x:si>
   <x:si>
-    <x:t>070-7014-8703</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-503-1020</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7096-6872</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-312-3600</x:t>
-  </x:si>
-  <x:si>
-    <x:t>복특 6학급/ 시간제 2학급</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-4648-5770</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7016-3005</x:t>
+    <x:t>031-8042-2502</x:t>
   </x:si>
   <x:si>
     <x:t>한국글로벌중학구
 /소래중학구</x:t>
   </x:si>
   <x:si>
-    <x:t>031-8042-2502</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-364-3410</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8099-5900</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8042-0700</x:t>
-  </x:si>
-  <x:si>
-    <x:t>⊙연성초등학교 학구 중 목감동 1~2통, 3통 4반~6반은 목감중학구 및 안산시 안산중학구와 공동학구</x:t>
+    <x:t>070-7096-6083</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-0603</x:t>
   </x:si>
   <x:si>
     <x:t>⊙도창초등학교 학구 중 매화동 5통, 매화동 20~22통은 시흥매화중학구와 공동학구
@@ -255,472 +87,640 @@
 ⊙도창초등학교 학구 중 과림동 1통(노무저리 제외),  과림동 2통은 광명시 광명중학군과 공동학구</x:t>
   </x:si>
   <x:si>
-    <x:t>소래중학구/연성중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥가온초등학교</x:t>
-  </x:si>
-  <x:si>
     <x:t>경기도 시흥시 나분들길 44</x:t>
   </x:si>
   <x:si>
+    <x:t>031-8042-0700</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8099-5900</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-434-6152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-364-3410</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥신일초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧누리초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥매화초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥은행초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥월곶초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>목감중학구/조남중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧해솔초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시화나래초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥장현초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한국글로벌중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군서미래국제학교(초)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7015-4404</x:t>
+  </x:si>
+  <x:si>
+    <x:t>성인 · 주부 · 어르신</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-2915</x:t>
+  </x:si>
+  <x:si>
+    <x:t>복특 6학급/ 시간제 2학급</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8032-6504</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8099-9703</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-363-5904</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-365-8003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8040-6505</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 역전로 455</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(복합특수/시간제/일반)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-500-0601</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 포도원로 39</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 대골안길 31</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8085-7004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7096-7772</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-503-0560</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8063-7873</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7096-7706</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한여울초등학교(복합특수)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7096-7801</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-503-1538</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8044-1261</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-1108</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-1683</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-1303</x:t>
+  </x:si>
+  <x:si>
+    <x:t>계수초등학교 학구 중 계수동은 부천시 소사옥길중학군과 공동학구</x:t>
+  </x:si>
+  <x:si>
     <x:t>경기도 시흥시 승지로 110</x:t>
   </x:si>
   <x:si>
+    <x:t>031-364-7903</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-0802</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-312-3600</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-310-4695</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-363-1526</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-490-8204</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-2707</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 은행고길 18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-4648-5770</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7014-4072</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 군자로 539</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 옥터로 33</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-2576</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 능곡군자로 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-2302</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 매화1로 6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-363-3003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>목감중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정왕중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥매화중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소래중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>승지초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하중초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>은계초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21/ 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>은빛초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>진말초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장곡중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소래초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대야초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>생금초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도일초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연성초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>산현초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 목감초등길 49</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 목감둘레로 109</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 장곡로 70번길 12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 신천로 7번길 12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 배곧1로 28-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 배곧 4로 44-5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 목감남서로 68</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 서울대학로 255</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 대은로103번길 24</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">경기도 시흥시 은행동 663 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 중심상가로 257</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 죽율로 45-42</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 호현로 27번길 14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 군자로465번길 7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 군서마을로 101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 시청로80번길 5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 목감둘레로 229-9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 거북섬남로 70</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 큰솔로 7번길 10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 월곶중앙로 18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 대은로 16-29</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 장현능곡로 33</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 수인로2793번길 6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 월곶해안로 69</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 능곡중앙로 22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 배곧4로 94-39</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 황고개로 567</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 서울대학로 150-17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 해송십리로 472-30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 대은로 104번길 29-10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 정왕대로 143번길 15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 정왕천로427번길 30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 정왕대로 53번길 14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 수인로3247번길 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 하중로 209번길 10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 옥구천동로 433-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 수인로 3413번길 34</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 정왕대로118번길 27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 신현로 202번길 31</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8063-2903</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7016-3005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-2204</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 계수로 203</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한국글로벌중학구/ 소래중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-1553</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-494-4167</x:t>
+  </x:si>
+  <x:si>
     <x:t>경기도 시흥시 역전로 369</x:t>
   </x:si>
   <x:si>
-    <x:t>경기도 시흥시 옥터로 33</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-2576</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 능곡군자로 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-2302</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-363-3003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 매화1로 6</x:t>
-  </x:si>
-  <x:si>
     <x:t>031-364-1700</x:t>
   </x:si>
   <x:si>
-    <x:t>070-7097-1108</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-494-4167</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-1553</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8032-6504</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-434-6152</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-1303</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8085-7004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7096-7772</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8099-9703</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8040-6505</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-363-5904</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 역전로 455</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-365-8003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-500-0601</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(복합특수/시간제/일반)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 대골안길 31</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 포도원로 39</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥장현초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한국글로벌중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>군서미래국제학교(초)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧누리초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥신일초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥매화초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>계수초등학교 학구 중 계수동은 부천시 소사옥길중학군과 공동학구</x:t>
+    <x:t>031-503-1020</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7096-6872</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>위도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공립</x:t>
+  </x:si>
+  <x:si>
+    <x:t>⊙목감초등학교 학구 중 목감동 4통, 6통은 안산중학구와 공동학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>진영초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연성중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신천초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15/ 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥능곡중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>월곶중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>월포초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수/순회)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>웃터골초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>송운초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서촌초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>포리초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>금모래초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>목감초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24/ 12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도창초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군서초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>냉정초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥터초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>함현초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>계수초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3학기제</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군자초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>조남초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>운흥초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장곡초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시화중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시화초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서해초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군자중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정왕초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>검바위초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 19명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 16명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 10명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 특수/순회학급수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보조인력 배치 유/무</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 2학급)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 6명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 14명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 13명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 5명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 21명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 1학급)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 8명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 4학급)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 22명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 3학급)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 4명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 2명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 7명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 18명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 17명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 9명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 11명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 15명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 20명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수 : 23명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 연락처</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 학교명</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 학교설립별</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16/ 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일반학급 배치 학생 수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>특수/순회학급 배치 학생 수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5명</x:t>
   </x:si>
   <x:si>
     <x:t>1명</x:t>
   </x:si>
   <x:si>
-    <x:t>서해초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정왕초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>검바위초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정왕중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥매화중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>목감중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하중초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>승지초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소래중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연성초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>은빛초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>산현초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>은계초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21/ 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>진말초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소래초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대야초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장곡중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>생금초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도일초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연성중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15/ 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>신천초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥능곡중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>진영초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>웃터골초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수/순회)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>월곶중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>월포초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>포리초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>송운초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>서촌초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도창초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>목감초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>금모래초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>군서초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24/ 12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>함현초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>냉정초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>계수초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥터초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>군자초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3학기제</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장곡초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>운흥초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16/ 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>조남초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시화초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시화중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>군자중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥은행초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧해솔초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥월곶초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시화나래초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>목감중학구/조남중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 서울대학로 255</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 대은로103번길 24</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 호현로 27번길 14</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">경기도 시흥시 은행동 663 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 죽율로 45-42</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 중심상가로 257</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 시청로80번길 5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 거북섬남로 70</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 목감둘레로 229-9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 군자로465번길 7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 군서마을로 101</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 월곶중앙로 18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 수인로2793번길 6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 큰솔로 7번길 10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 대은로 16-29</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 장현능곡로 33</x:t>
-  </x:si>
-  <x:si>
-    <x:t>⊙목감초등학교 학구 중 목감동 4통, 6통은 안산중학구와 공동학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>위도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수/순회/일반)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧라온초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥능곡초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥도원초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧라라초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧한울초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 19명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 2학급)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 6명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 13명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 16명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 10명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 특수/순회학급수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보조인력 배치 유/무</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 14명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 8명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 21명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 5명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 1학급)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 3학급)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 4명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 4학급)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 22명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 7명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 18명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 2명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 17명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 9명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 11명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 15명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 20명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수 : 23명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5명</x:t>
-  </x:si>
-  <x:si>
     <x:t>10명</x:t>
   </x:si>
   <x:si>
+    <x:t>4명</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 비고</x:t>
+  </x:si>
+  <x:si>
     <x:t>2명</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve"> 연락처</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 학교명</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 학교설립별</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일반학급 배치 학생 수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>특수/순회학급 배치 학생 수</x:t>
+    <x:t xml:space="preserve"> 학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13명</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 주소</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3명</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1135,73 +1135,74 @@
     <x:col min="6" max="6" width="27.62890625" customWidth="1"/>
     <x:col min="7" max="7" width="24.55078125" bestFit="1" customWidth="1"/>
     <x:col min="8" max="8" width="19.9921875" bestFit="1" customWidth="1"/>
+    <x:col min="11" max="12" width="11.51171875" bestFit="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:12">
       <x:c r="A1" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="B1" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="C1" t="s">
         <x:v>228</x:v>
       </x:c>
-      <x:c r="B1" t="s">
-        <x:v>229</x:v>
-      </x:c>
-      <x:c r="C1" t="s">
-        <x:v>52</x:v>
-      </x:c>
       <x:c r="D1" t="s">
-        <x:v>53</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="E1" t="s">
-        <x:v>227</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F1" t="s">
-        <x:v>204</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="G1" t="s">
-        <x:v>232</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="H1" t="s">
-        <x:v>231</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="I1" t="s">
-        <x:v>205</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="J1" t="s">
-        <x:v>54</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="K1" t="s">
-        <x:v>191</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="L1" t="s">
-        <x:v>190</x:v>
+        <x:v>149</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:12" ht="65.5">
       <x:c r="A2" t="s">
-        <x:v>116</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="B2" t="s">
-        <x:v>51</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D2" t="s">
-        <x:v>28</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="E2" t="s">
-        <x:v>18</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F2" t="s">
-        <x:v>211</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="G2" t="s">
-        <x:v>208</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="H2" t="s">
-        <x:v>0</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="I2" t="s">
-        <x:v>189</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="K2">
         <x:v>37.432746760000001</x:v>
@@ -1212,34 +1213,34 @@
     </x:row>
     <x:row r="3" spans="1:12">
       <x:c r="A3" t="s">
-        <x:v>154</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="B3" t="s">
-        <x:v>51</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C3" t="s">
-        <x:v>107</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D3" t="s">
-        <x:v>15</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="E3" t="s">
-        <x:v>19</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F3" t="s">
-        <x:v>210</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="G3" t="s">
-        <x:v>212</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="H3" t="s">
-        <x:v>113</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="I3" t="s">
-        <x:v>50</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="J3" t="s">
-        <x:v>112</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K3">
         <x:v>37.453471950000001</x:v>
@@ -1250,31 +1251,31 @@
     </x:row>
     <x:row r="4" spans="1:12">
       <x:c r="A4" t="s">
-        <x:v>108</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B4" t="s">
-        <x:v>51</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C4" t="s">
-        <x:v>50</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="D4" t="s">
-        <x:v>182</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E4" t="s">
-        <x:v>2</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F4" t="s">
-        <x:v>50</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="G4" t="s">
-        <x:v>50</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="H4" t="s">
-        <x:v>0</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="I4" t="s">
-        <x:v>50</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="K4">
         <x:v>37.34626506</x:v>
@@ -1285,31 +1286,31 @@
     </x:row>
     <x:row r="5" spans="1:12">
       <x:c r="A5" t="s">
-        <x:v>150</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="B5" t="s">
-        <x:v>51</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C5" t="s">
-        <x:v>117</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D5" t="s">
-        <x:v>26</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="E5" t="s">
-        <x:v>71</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F5" t="s">
-        <x:v>211</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="G5" t="s">
-        <x:v>214</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="H5" t="s">
-        <x:v>224</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="I5" t="s">
-        <x:v>189</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="K5">
         <x:v>37.347420020000001</x:v>
@@ -1320,31 +1321,31 @@
     </x:row>
     <x:row r="6" spans="1:12">
       <x:c r="A6" t="s">
-        <x:v>157</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="B6" t="s">
-        <x:v>51</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C6" t="s">
-        <x:v>166</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="D6" t="s">
-        <x:v>41</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E6" t="s">
-        <x:v>68</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F6" t="s">
-        <x:v>213</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="G6" t="s">
-        <x:v>208</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="H6" t="s">
-        <x:v>113</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="I6" t="s">
-        <x:v>189</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="K6">
         <x:v>37.343899370000003</x:v>
@@ -1355,31 +1356,31 @@
     </x:row>
     <x:row r="7" spans="1:12" ht="65.5">
       <x:c r="A7" t="s">
-        <x:v>149</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="B7" t="s">
-        <x:v>51</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D7" t="s">
-        <x:v>186</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E7" t="s">
-        <x:v>57</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F7" t="s">
-        <x:v>199</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="G7" t="s">
-        <x:v>201</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="H7" t="s">
-        <x:v>224</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="I7" t="s">
-        <x:v>189</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="K7">
         <x:v>37.441589</x:v>
@@ -1390,31 +1391,31 @@
     </x:row>
     <x:row r="8" spans="1:12">
       <x:c r="A8" t="s">
-        <x:v>153</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="B8" t="s">
-        <x:v>51</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C8" t="s">
-        <x:v>117</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D8" t="s">
-        <x:v>81</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E8" t="s">
-        <x:v>74</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F8" t="s">
-        <x:v>211</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="G8" t="s">
-        <x:v>198</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="H8" t="s">
-        <x:v>0</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="I8" t="s">
-        <x:v>189</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="K8">
         <x:v>37.357741859999997</x:v>
@@ -1425,31 +1426,31 @@
     </x:row>
     <x:row r="9" spans="1:12">
       <x:c r="A9" t="s">
-        <x:v>130</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B9" t="s">
-        <x:v>51</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C9" t="s">
-        <x:v>14</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D9" t="s">
-        <x:v>104</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E9" t="s">
-        <x:v>86</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="F9" t="s">
-        <x:v>211</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="G9" t="s">
-        <x:v>202</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="H9" t="s">
-        <x:v>226</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="I9" t="s">
-        <x:v>50</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="K9">
         <x:v>37.446825369999999</x:v>
@@ -1460,19 +1461,19 @@
     </x:row>
     <x:row r="10" spans="1:12">
       <x:c r="A10" t="s">
-        <x:v>134</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B10" t="s">
-        <x:v>51</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C10" t="s">
-        <x:v>166</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="D10" t="s">
-        <x:v>181</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="E10" t="s">
-        <x:v>90</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="F10" s="2">
         <x:v>46054</x:v>
@@ -1481,13 +1482,13 @@
         <x:v>46268</x:v>
       </x:c>
       <x:c r="H10" t="s">
-        <x:v>50</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="I10" t="s">
-        <x:v>50</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="J10" t="s">
-        <x:v>141</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="K10">
         <x:v>37.349119160000001</x:v>
@@ -1498,22 +1499,22 @@
     </x:row>
     <x:row r="11" spans="1:12" ht="409.5">
       <x:c r="A11" t="s">
-        <x:v>147</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="B11" t="s">
-        <x:v>51</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D11" t="s">
-        <x:v>184</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="E11" t="s">
-        <x:v>85</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F11" t="s">
-        <x:v>50</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="G11">
         <x:v>0</x:v>
@@ -1522,10 +1523,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I11" t="s">
-        <x:v>50</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="J11" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K11">
         <x:v>37.406893609999997</x:v>
@@ -1536,34 +1537,34 @@
     </x:row>
     <x:row r="12" spans="1:12">
       <x:c r="A12" t="s">
-        <x:v>148</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="B12" t="s">
-        <x:v>51</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C12" t="s">
-        <x:v>119</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D12" t="s">
-        <x:v>9</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E12" t="s">
-        <x:v>91</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="F12" t="s">
-        <x:v>199</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="G12" t="s">
-        <x:v>203</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H12" t="s">
-        <x:v>50</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="I12" t="s">
-        <x:v>189</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="J12" t="s">
-        <x:v>188</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="K12">
         <x:v>37.386862639999997</x:v>
@@ -1574,31 +1575,31 @@
     </x:row>
     <x:row r="13" spans="1:12">
       <x:c r="A13" t="s">
-        <x:v>109</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B13" t="s">
-        <x:v>51</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C13" t="s">
-        <x:v>132</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="D13" t="s">
-        <x:v>20</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="E13" t="s">
-        <x:v>45</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="F13" t="s">
-        <x:v>213</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="G13" t="s">
-        <x:v>208</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="H13" s="3" t="s">
-        <x:v>224</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="I13" t="s">
-        <x:v>189</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="K13">
         <x:v>37.382653580000003</x:v>
@@ -1609,31 +1610,31 @@
     </x:row>
     <x:row r="14" spans="1:12">
       <x:c r="A14" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B14" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="C14" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="D14" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="E14" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="F14" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="G14" t="s">
         <x:v>196</x:v>
       </x:c>
-      <x:c r="B14" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C14" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="D14" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="E14" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="F14" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="G14" t="s">
-        <x:v>200</x:v>
-      </x:c>
       <x:c r="H14" s="3" t="s">
-        <x:v>226</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="I14" t="s">
-        <x:v>50</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="K14">
         <x:v>37.369258219999999</x:v>
@@ -1644,31 +1645,31 @@
     </x:row>
     <x:row r="15" spans="1:12">
       <x:c r="A15" t="s">
-        <x:v>193</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B15" t="s">
-        <x:v>51</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C15" t="s">
-        <x:v>132</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="D15" t="s">
-        <x:v>3</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E15" t="s">
-        <x:v>92</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F15" t="s">
-        <x:v>211</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="G15" t="s">
-        <x:v>222</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="H15" s="3" t="s">
-        <x:v>226</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="I15" t="s">
-        <x:v>189</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="K15">
         <x:v>37.372575730000001</x:v>
@@ -1679,31 +1680,31 @@
     </x:row>
     <x:row r="16" spans="1:12">
       <x:c r="A16" t="s">
-        <x:v>160</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="B16" t="s">
-        <x:v>51</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C16" t="s">
-        <x:v>132</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="D16" t="s">
-        <x:v>10</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E16" t="s">
-        <x:v>97</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F16" t="s">
-        <x:v>199</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="G16" t="s">
-        <x:v>221</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="H16" s="3" t="s">
-        <x:v>224</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="I16" t="s">
-        <x:v>189</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="K16">
         <x:v>37.376015750000001</x:v>
@@ -1714,31 +1715,31 @@
     </x:row>
     <x:row r="17" spans="1:12">
       <x:c r="A17" t="s">
-        <x:v>197</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B17" t="s">
-        <x:v>51</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C17" t="s">
-        <x:v>132</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="D17" t="s">
-        <x:v>13</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E17" t="s">
-        <x:v>62</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F17" t="s">
-        <x:v>211</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="G17" t="s">
-        <x:v>198</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="H17" t="s">
-        <x:v>50</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="I17" t="s">
-        <x:v>189</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="K17">
         <x:v>37.360501769999999</x:v>
@@ -1749,31 +1750,31 @@
     </x:row>
     <x:row r="18" spans="1:12">
       <x:c r="A18" t="s">
-        <x:v>168</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B18" t="s">
-        <x:v>51</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C18" t="s">
-        <x:v>132</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="D18" t="s">
-        <x:v>21</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="E18" t="s">
-        <x:v>17</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F18" t="s">
-        <x:v>199</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="G18" t="s">
-        <x:v>220</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H18" t="s">
-        <x:v>224</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="I18" t="s">
-        <x:v>189</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="K18">
         <x:v>37.360535210000002</x:v>
@@ -1784,31 +1785,31 @@
     </x:row>
     <x:row r="19" spans="1:12">
       <x:c r="A19" t="s">
-        <x:v>125</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B19" t="s">
-        <x:v>51</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C19" t="s">
-        <x:v>171</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D19" t="s">
-        <x:v>12</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E19" t="s">
-        <x:v>98</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F19" t="s">
-        <x:v>199</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="G19" t="s">
-        <x:v>201</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="H19" t="s">
-        <x:v>50</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="I19" t="s">
-        <x:v>189</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="K19">
         <x:v>37.37494805</x:v>
@@ -1819,31 +1820,31 @@
     </x:row>
     <x:row r="20" spans="1:12">
       <x:c r="A20" t="s">
-        <x:v>133</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B20" t="s">
-        <x:v>51</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C20" t="s">
-        <x:v>117</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D20" t="s">
-        <x:v>176</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E20" t="s">
-        <x:v>69</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="F20" t="s">
-        <x:v>210</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="G20" t="s">
-        <x:v>209</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="H20" t="s">
-        <x:v>224</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="I20" t="s">
-        <x:v>50</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="K20">
         <x:v>37.350397829999999</x:v>
@@ -1854,31 +1855,31 @@
     </x:row>
     <x:row r="21" spans="1:12">
       <x:c r="A21" t="s">
-        <x:v>146</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="B21" t="s">
-        <x:v>51</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C21" t="s">
-        <x:v>117</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D21" t="s">
-        <x:v>29</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="E21" t="s">
-        <x:v>46</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F21" t="s">
-        <x:v>199</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="G21" t="s">
-        <x:v>201</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="H21" t="s">
-        <x:v>113</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="I21" t="s">
-        <x:v>189</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="K21">
         <x:v>37.349460039999997</x:v>
@@ -1889,34 +1890,34 @@
     </x:row>
     <x:row r="22" spans="1:12">
       <x:c r="A22" t="s">
-        <x:v>114</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="B22" t="s">
-        <x:v>51</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C22" t="s">
-        <x:v>117</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D22" t="s">
-        <x:v>27</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E22" t="s">
-        <x:v>93</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F22" s="2">
         <x:v>46082</x:v>
       </x:c>
       <x:c r="G22" t="s">
-        <x:v>162</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="H22" t="s">
-        <x:v>113</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="I22" t="s">
-        <x:v>189</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="J22" t="s">
-        <x:v>192</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K22">
         <x:v>37.356151019999999</x:v>
@@ -1927,31 +1928,31 @@
     </x:row>
     <x:row r="23" spans="1:12">
       <x:c r="A23" t="s">
-        <x:v>129</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B23" t="s">
-        <x:v>51</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C23" t="s">
-        <x:v>122</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D23" t="s">
-        <x:v>174</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E23" t="s">
-        <x:v>37</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F23" t="s">
-        <x:v>199</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="G23" t="s">
-        <x:v>207</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="H23" t="s">
-        <x:v>113</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="I23" t="s">
-        <x:v>189</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="K23">
         <x:v>37.443772459999998</x:v>
@@ -1962,31 +1963,31 @@
     </x:row>
     <x:row r="24" spans="1:12">
       <x:c r="A24" t="s">
-        <x:v>145</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="B24" t="s">
-        <x:v>51</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C24" t="s">
-        <x:v>117</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D24" t="s">
-        <x:v>24</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="E24" t="s">
-        <x:v>102</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F24" t="s">
-        <x:v>199</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="G24" t="s">
-        <x:v>206</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="H24" t="s">
-        <x:v>230</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="I24" t="s">
-        <x:v>189</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="K24">
         <x:v>35.228763190000002</x:v>
@@ -1997,31 +1998,31 @@
     </x:row>
     <x:row r="25" spans="1:12">
       <x:c r="A25" t="s">
-        <x:v>121</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B25" t="s">
-        <x:v>51</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C25" t="s">
-        <x:v>138</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="D25" t="s">
-        <x:v>80</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E25" t="s">
-        <x:v>73</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F25" t="s">
-        <x:v>199</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="G25" t="s">
-        <x:v>220</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H25" t="s">
-        <x:v>230</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="I25" t="s">
-        <x:v>189</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="K25">
         <x:v>37.372313550000001</x:v>
@@ -2032,31 +2033,31 @@
     </x:row>
     <x:row r="26" spans="1:12">
       <x:c r="A26" t="s">
-        <x:v>170</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B26" t="s">
-        <x:v>51</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C26" t="s">
-        <x:v>165</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="D26" t="s">
-        <x:v>179</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E26" t="s">
-        <x:v>72</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F26" t="s">
-        <x:v>199</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="G26" t="s">
-        <x:v>206</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="H26" t="s">
-        <x:v>32</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="I26" t="s">
-        <x:v>189</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="K26">
         <x:v>37.320716019999999</x:v>
@@ -2067,31 +2068,31 @@
     </x:row>
     <x:row r="27" spans="1:12">
       <x:c r="A27" t="s">
-        <x:v>164</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="B27" t="s">
-        <x:v>51</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C27" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D27" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="D27" t="s">
-        <x:v>185</x:v>
-      </x:c>
       <x:c r="E27" t="s">
-        <x:v>35</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F27" t="s">
-        <x:v>199</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="G27" t="s">
-        <x:v>221</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="H27" t="s">
-        <x:v>226</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="I27" t="s">
-        <x:v>189</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="K27">
         <x:v>37.339255610000002</x:v>
@@ -2102,31 +2103,31 @@
     </x:row>
     <x:row r="28" spans="1:12">
       <x:c r="A28" t="s">
-        <x:v>78</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B28" t="s">
-        <x:v>51</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C28" t="s">
-        <x:v>131</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D28" t="s">
-        <x:v>187</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E28" t="s">
-        <x:v>88</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="F28" t="s">
-        <x:v>211</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="G28" t="s">
-        <x:v>223</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="H28" s="3" t="s">
-        <x:v>230</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="I28" t="s">
-        <x:v>189</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="K28">
         <x:v>37.37378717</x:v>
@@ -2137,31 +2138,31 @@
     </x:row>
     <x:row r="29" spans="1:12">
       <x:c r="A29" t="s">
-        <x:v>194</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B29" t="s">
-        <x:v>51</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C29" t="s">
-        <x:v>138</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="D29" t="s">
-        <x:v>5</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="E29" t="s">
-        <x:v>65</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="F29" t="s">
-        <x:v>199</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="G29" t="s">
-        <x:v>203</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H29" s="3" t="s">
-        <x:v>113</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="I29" t="s">
-        <x:v>50</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="K29">
         <x:v>37.365372309999998</x:v>
@@ -2172,31 +2173,31 @@
     </x:row>
     <x:row r="30" spans="1:12">
       <x:c r="A30" t="s">
-        <x:v>195</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B30" t="s">
-        <x:v>51</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C30" t="s">
-        <x:v>122</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D30" t="s">
-        <x:v>30</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="E30" t="s">
-        <x:v>89</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F30" t="s">
-        <x:v>210</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="G30" t="s">
-        <x:v>212</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="H30" s="3" t="s">
-        <x:v>113</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="I30" t="s">
-        <x:v>50</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="K30">
         <x:v>37.440093009999998</x:v>
@@ -2207,31 +2208,31 @@
     </x:row>
     <x:row r="31" spans="1:12">
       <x:c r="A31" t="s">
-        <x:v>111</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B31" t="s">
-        <x:v>51</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C31" t="s">
-        <x:v>118</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D31" t="s">
-        <x:v>87</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E31" t="s">
-        <x:v>47</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F31" t="s">
-        <x:v>211</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="G31" t="s">
-        <x:v>218</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="H31" t="s">
-        <x:v>50</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="I31" t="s">
-        <x:v>50</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="K31">
         <x:v>37.416300909999997</x:v>
@@ -2242,31 +2243,31 @@
     </x:row>
     <x:row r="32" spans="1:12">
       <x:c r="A32" t="s">
-        <x:v>110</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B32" t="s">
-        <x:v>51</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C32" t="s">
-        <x:v>122</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D32" t="s">
-        <x:v>11</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E32" t="s">
-        <x:v>61</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F32" t="s">
-        <x:v>199</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="G32" t="s">
-        <x:v>207</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="H32" t="s">
-        <x:v>226</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="I32" t="s">
-        <x:v>50</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="K32">
         <x:v>37.433075209999998</x:v>
@@ -2277,31 +2278,31 @@
     </x:row>
     <x:row r="33" spans="1:12">
       <x:c r="A33" t="s">
-        <x:v>169</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B33" t="s">
-        <x:v>51</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C33" t="s">
-        <x:v>142</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="D33" t="s">
-        <x:v>4</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E33" t="s">
-        <x:v>39</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F33" t="s">
-        <x:v>199</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="G33" t="s">
-        <x:v>219</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="H33" t="s">
-        <x:v>230</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="I33" t="s">
-        <x:v>189</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="K33">
         <x:v>37.391718959999999</x:v>
@@ -2312,31 +2313,31 @@
     </x:row>
     <x:row r="34" spans="1:12" ht="65.5">
       <x:c r="A34" t="s">
-        <x:v>167</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B34" t="s">
-        <x:v>51</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D34" t="s">
-        <x:v>22</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E34" t="s">
-        <x:v>48</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F34" t="s">
-        <x:v>211</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="G34" t="s">
-        <x:v>216</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H34" t="s">
-        <x:v>226</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="I34" t="s">
-        <x:v>50</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="K34">
         <x:v>37.442591470000004</x:v>
@@ -2347,31 +2348,31 @@
     </x:row>
     <x:row r="35" spans="1:12">
       <x:c r="A35" t="s">
-        <x:v>106</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B35" t="s">
-        <x:v>51</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C35" t="s">
-        <x:v>131</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D35" t="s">
-        <x:v>178</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="E35" t="s">
-        <x:v>1</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F35" t="s">
-        <x:v>199</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="G35" t="s">
-        <x:v>219</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="H35" t="s">
-        <x:v>230</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="I35" t="s">
-        <x:v>189</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="K35">
         <x:v>37.381790879999997</x:v>
@@ -2382,31 +2383,31 @@
     </x:row>
     <x:row r="36" spans="1:12">
       <x:c r="A36" t="s">
-        <x:v>156</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="B36" t="s">
-        <x:v>51</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C36" t="s">
-        <x:v>117</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D36" t="s">
-        <x:v>23</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="E36" t="s">
-        <x:v>58</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F36" t="s">
-        <x:v>211</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="G36" t="s">
-        <x:v>216</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="H36" t="s">
-        <x:v>0</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="I36" t="s">
-        <x:v>189</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="K36">
         <x:v>33.479625749999997</x:v>
@@ -2417,31 +2418,31 @@
     </x:row>
     <x:row r="37" spans="1:12">
       <x:c r="A37" t="s">
-        <x:v>137</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="B37" t="s">
-        <x:v>51</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C37" t="s">
-        <x:v>122</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D37" t="s">
-        <x:v>60</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E37" t="s">
-        <x:v>38</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F37" t="s">
-        <x:v>199</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="G37" t="s">
-        <x:v>220</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H37" t="s">
-        <x:v>50</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="I37" t="s">
-        <x:v>50</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="K37">
         <x:v>37.43524335</x:v>
@@ -2452,34 +2453,34 @@
     </x:row>
     <x:row r="38" spans="1:12">
       <x:c r="A38" t="s">
-        <x:v>123</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B38" t="s">
-        <x:v>51</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C38" t="s">
-        <x:v>119</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D38" t="s">
-        <x:v>79</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E38" t="s">
-        <x:v>63</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F38" t="s">
-        <x:v>199</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="G38" t="s">
-        <x:v>207</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="H38" t="s">
-        <x:v>50</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="I38" t="s">
-        <x:v>189</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="J38" t="s">
-        <x:v>75</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K38">
         <x:v>37.387563890000003</x:v>
@@ -2490,31 +2491,31 @@
     </x:row>
     <x:row r="39" spans="1:12">
       <x:c r="A39" t="s">
-        <x:v>155</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="B39" t="s">
-        <x:v>51</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C39" t="s">
-        <x:v>117</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D39" t="s">
-        <x:v>82</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E39" t="s">
-        <x:v>56</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F39" t="s">
-        <x:v>199</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="G39" t="s">
-        <x:v>221</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="H39" t="s">
-        <x:v>50</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="I39" t="s">
-        <x:v>189</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="K39">
         <x:v>37.345110460000001</x:v>
@@ -2525,31 +2526,31 @@
     </x:row>
     <x:row r="40" spans="1:12">
       <x:c r="A40" t="s">
-        <x:v>161</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B40" t="s">
-        <x:v>51</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C40" t="s">
-        <x:v>171</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D40" t="s">
-        <x:v>7</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E40" t="s">
-        <x:v>99</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F40" t="s">
-        <x:v>199</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="G40" t="s">
-        <x:v>206</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="H40" t="s">
-        <x:v>225</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="I40" t="s">
-        <x:v>189</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="K40">
         <x:v>37.372765039999997</x:v>
@@ -2560,31 +2561,31 @@
     </x:row>
     <x:row r="41" spans="1:12" ht="65.5">
       <x:c r="A41" t="s">
-        <x:v>140</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="B41" t="s">
-        <x:v>51</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D41" t="s">
-        <x:v>44</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E41" t="s">
-        <x:v>34</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F41" t="s">
-        <x:v>199</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="G41" t="s">
-        <x:v>219</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="H41" t="s">
-        <x:v>226</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="I41" t="s">
-        <x:v>189</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="K41">
         <x:v>37.439720010000002</x:v>
@@ -2595,31 +2596,31 @@
     </x:row>
     <x:row r="42" spans="1:12">
       <x:c r="A42" t="s">
-        <x:v>143</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="B42" t="s">
-        <x:v>51</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C42" t="s">
-        <x:v>142</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="D42" t="s">
-        <x:v>183</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E42" t="s">
-        <x:v>42</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F42" t="s">
-        <x:v>199</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="G42" t="s">
-        <x:v>219</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="H42" t="s">
-        <x:v>113</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="I42" t="s">
-        <x:v>189</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="K42">
         <x:v>37.387488849999997</x:v>
@@ -2630,34 +2631,34 @@
     </x:row>
     <x:row r="43" spans="1:12" ht="65.5">
       <x:c r="A43" t="s">
-        <x:v>126</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B43" t="s">
-        <x:v>51</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D43" t="s">
-        <x:v>173</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E43" t="s">
-        <x:v>96</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F43" s="2">
         <x:v>46082</x:v>
       </x:c>
       <x:c r="G43" t="s">
-        <x:v>136</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="H43" t="s">
-        <x:v>0</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="I43" t="s">
-        <x:v>189</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="J43" t="s">
-        <x:v>192</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K43">
         <x:v>37.44773309</x:v>
@@ -2668,31 +2669,31 @@
     </x:row>
     <x:row r="44" spans="1:12" ht="65.5">
       <x:c r="A44" t="s">
-        <x:v>124</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B44" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="C44" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D44" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="E44" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C44" s="1" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="D44" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="E44" t="s">
-        <x:v>95</x:v>
-      </x:c>
       <x:c r="F44" t="s">
-        <x:v>211</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="G44" t="s">
-        <x:v>208</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="H44" t="s">
-        <x:v>0</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="I44" t="s">
-        <x:v>189</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="K44">
         <x:v>37.434280770000001</x:v>
@@ -2703,31 +2704,31 @@
     </x:row>
     <x:row r="45" spans="1:12">
       <x:c r="A45" t="s">
-        <x:v>159</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="B45" t="s">
-        <x:v>51</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C45" t="s">
-        <x:v>131</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D45" t="s">
-        <x:v>8</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E45" t="s">
-        <x:v>55</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F45" t="s">
-        <x:v>211</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="G45" t="s">
-        <x:v>206</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="H45" t="s">
-        <x:v>113</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="I45" t="s">
-        <x:v>189</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="K45">
         <x:v>37.381523569999999</x:v>
@@ -2738,34 +2739,34 @@
     </x:row>
     <x:row r="46" spans="1:12">
       <x:c r="A46" t="s">
-        <x:v>115</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="B46" t="s">
-        <x:v>51</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C46" t="s">
-        <x:v>117</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D46" t="s">
-        <x:v>177</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E46" t="s">
-        <x:v>16</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F46" s="2">
         <x:v>46082</x:v>
       </x:c>
       <x:c r="G46" t="s">
-        <x:v>127</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H46" t="s">
-        <x:v>0</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="I46" t="s">
-        <x:v>189</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="J46" t="s">
-        <x:v>192</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K46">
         <x:v>37.341022029999998</x:v>
@@ -2776,31 +2777,31 @@
     </x:row>
     <x:row r="47" spans="1:12">
       <x:c r="A47" t="s">
-        <x:v>163</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="B47" t="s">
-        <x:v>51</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C47" t="s">
-        <x:v>171</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D47" t="s">
-        <x:v>180</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E47" t="s">
-        <x:v>43</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F47" t="s">
-        <x:v>199</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="G47" t="s">
-        <x:v>206</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="H47" t="s">
-        <x:v>226</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="I47" t="s">
-        <x:v>189</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="K47">
         <x:v>37.378656040000003</x:v>
@@ -2811,31 +2812,31 @@
     </x:row>
     <x:row r="48" spans="1:12">
       <x:c r="A48" t="s">
-        <x:v>128</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B48" t="s">
-        <x:v>51</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C48" t="s">
-        <x:v>131</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D48" t="s">
-        <x:v>6</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E48" t="s">
-        <x:v>49</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F48" t="s">
-        <x:v>211</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="G48" t="s">
-        <x:v>222</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="H48" t="s">
-        <x:v>33</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="I48" t="s">
-        <x:v>189</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="K48">
         <x:v>37.38076332</x:v>
@@ -2846,34 +2847,34 @@
     </x:row>
     <x:row r="49" spans="1:12">
       <x:c r="A49" t="s">
-        <x:v>139</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="B49" t="s">
-        <x:v>158</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C49" t="s">
-        <x:v>50</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="D49" t="s">
-        <x:v>105</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E49" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F49" t="s">
-        <x:v>50</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="G49" t="s">
-        <x:v>50</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="H49" t="s">
-        <x:v>50</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="I49" t="s">
-        <x:v>50</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="J49" t="s">
-        <x:v>59</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="K49">
         <x:v>37.436062530000001</x:v>
@@ -2884,31 +2885,31 @@
     </x:row>
     <x:row r="50" spans="1:12">
       <x:c r="A50" t="s">
-        <x:v>144</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="B50" t="s">
-        <x:v>51</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C50" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D50" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="E50" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="D50" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E50" t="s">
-        <x:v>83</x:v>
-      </x:c>
       <x:c r="F50" t="s">
-        <x:v>210</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="G50" t="s">
-        <x:v>217</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="H50" t="s">
-        <x:v>50</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="I50" t="s">
-        <x:v>50</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="K50">
         <x:v>37.405642800000003</x:v>
@@ -2919,31 +2920,31 @@
     </x:row>
     <x:row r="51" spans="1:12">
       <x:c r="A51" t="s">
-        <x:v>120</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B51" t="s">
-        <x:v>51</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C51" t="s">
-        <x:v>135</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="D51" t="s">
-        <x:v>25</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="E51" t="s">
-        <x:v>94</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F51" t="s">
-        <x:v>211</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="G51" t="s">
-        <x:v>221</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="H51" t="s">
-        <x:v>50</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="I51" t="s">
-        <x:v>189</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="K51">
         <x:v>37.393327390000003</x:v>
@@ -2954,34 +2955,34 @@
     </x:row>
     <x:row r="52" spans="1:12">
       <x:c r="A52" t="s">
-        <x:v>36</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B52" t="s">
-        <x:v>51</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C52" t="s">
-        <x:v>131</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D52" t="s">
-        <x:v>84</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E52" t="s">
-        <x:v>101</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F52" t="s">
-        <x:v>67</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G52" t="s">
-        <x:v>151</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="H52" t="s">
-        <x:v>226</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="I52" t="s">
-        <x:v>189</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="J52" t="s">
-        <x:v>103</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K52">
         <x:v>37.36561434</x:v>
@@ -2992,31 +2993,31 @@
     </x:row>
     <x:row r="53" spans="1:12">
       <x:c r="A53" t="s">
-        <x:v>152</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="B53" t="s">
-        <x:v>51</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C53" t="s">
-        <x:v>117</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D53" t="s">
-        <x:v>100</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E53" t="s">
-        <x:v>40</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F53" t="s">
-        <x:v>210</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="G53" t="s">
-        <x:v>215</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="H53" t="s">
-        <x:v>113</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="I53" t="s">
-        <x:v>50</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="K53">
         <x:v>37.365442260000002</x:v>
@@ -3026,7 +3027,7 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51166665554046630859" footer="0.51166665554046630859"/>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51152777671813964844" footer="0.51152777671813964844"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1"/>
 </x:worksheet>

--- a/data/elementary.xlsx
+++ b/data/elementary.xlsx
@@ -19,9 +19,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="204">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="208">
   <x:si>
     <x:t>⊙연성초등학교 학구 중 목감동 1~2통, 3통 4반~6반은 목감중학구 및 안산시 안산중학구와 공동학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보조인력 배치 유/무</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 특수/순회학급수</x:t>
   </x:si>
   <x:si>
     <x:t>031-364-1700</x:t>
@@ -74,15 +80,6 @@
     <x:t>031-503-1538</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve"> 주소</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 비고</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 학구</x:t>
-  </x:si>
-  <x:si>
     <x:t>계수초등학교 학구 중 계수동은 부천시 소사옥길중학군과 공동학구</x:t>
   </x:si>
   <x:si>
@@ -615,25 +612,48 @@
     <x:t>3학기제</x:t>
   </x:si>
   <x:si>
+    <x:r>
+      <x:t>126.730065</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 비고</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 주소</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 학구</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:t>37.360228,</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:t>126.72</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:t>37.34</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 학교설립별</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 연락처</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 학교명</x:t>
+  </x:si>
+  <x:si>
     <x:t>특수/순회학급 배치 학생 수</x:t>
   </x:si>
   <x:si>
     <x:t>일반학급 배치 학생 수</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 특수/순회학급수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보조인력 배치 유/무</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 학교설립별</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 연락처</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 학교명</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -771,7 +791,7 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="20">
+  <x:cellXfs count="21">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -922,6 +942,9 @@
         </x:xf>
       </mc:Fallback>
     </mc:AlternateContent>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="표준" xfId="0" builtinId="0" iLevel="0"/>
@@ -1255,57 +1278,57 @@
   <x:sheetData>
     <x:row r="1" spans="1:12">
       <x:c r="A1" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="B1" t="s">
         <x:v>203</x:v>
       </x:c>
-      <x:c r="B1" t="s">
-        <x:v>201</x:v>
-      </x:c>
       <x:c r="C1" t="s">
-        <x:v>19</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="D1" t="s">
-        <x:v>17</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="E1" t="s">
-        <x:v>202</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="F1" t="s">
-        <x:v>199</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G1" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="H1" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="I1" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J1" t="s">
         <x:v>197</x:v>
       </x:c>
-      <x:c r="H1" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="I1" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="J1" t="s">
-        <x:v>18</x:v>
-      </x:c>
       <x:c r="K1" t="s">
-        <x:v>136</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="L1" t="s">
-        <x:v>135</x:v>
+        <x:v>134</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A2" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F2" s="2">
         <x:v>3</x:v>
@@ -1317,7 +1340,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I2" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="J2" s="5"/>
       <x:c r="K2" s="5">
@@ -1329,19 +1352,19 @@
     </x:row>
     <x:row r="3" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A3" s="1" t="s">
-        <x:v>186</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F3" s="6">
         <x:v>1</x:v>
@@ -1353,10 +1376,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I3" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="J3" s="5" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="K3" s="5">
         <x:v>37.453471946211501</x:v>
@@ -1367,19 +1390,19 @@
     </x:row>
     <x:row r="4" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A4" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="C4" s="1" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="C4" s="1" t="s">
-        <x:v>138</x:v>
-      </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F4" s="7">
         <x:v>0</x:v>
@@ -1391,7 +1414,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I4" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="J4" s="5"/>
       <x:c r="K4" s="5">
@@ -1403,19 +1426,19 @@
     </x:row>
     <x:row r="5" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A5" s="1" t="s">
-        <x:v>179</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F5" s="6">
         <x:v>3</x:v>
@@ -1427,7 +1450,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I5" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="J5" s="5"/>
       <x:c r="K5" s="5">
@@ -1439,19 +1462,19 @@
     </x:row>
     <x:row r="6" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A6" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F6" s="6">
         <x:v>4</x:v>
@@ -1463,7 +1486,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I6" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="J6" s="5"/>
       <x:c r="K6" s="5">
@@ -1475,19 +1498,19 @@
     </x:row>
     <x:row r="7" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A7" s="1" t="s">
-        <x:v>189</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F7" s="6">
         <x:v>2</x:v>
@@ -1499,7 +1522,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I7" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="J7" s="5"/>
       <x:c r="K7" s="5">
@@ -1511,19 +1534,19 @@
     </x:row>
     <x:row r="8" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A8" s="1" t="s">
-        <x:v>190</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F8" s="6">
         <x:v>3</x:v>
@@ -1535,7 +1558,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I8" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="J8" s="5"/>
       <x:c r="K8" s="5">
@@ -1547,19 +1570,19 @@
     </x:row>
     <x:row r="9" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A9" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F9" s="6">
         <x:v>3</x:v>
@@ -1571,7 +1594,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I9" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="J9" s="5"/>
       <x:c r="K9" s="5">
@@ -1583,34 +1606,34 @@
     </x:row>
     <x:row r="10" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A10" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F10" s="8" t="s">
-        <x:v>169</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="G10" s="9" t="s">
-        <x:v>187</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="H10" s="3">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I10" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="J10" s="5" t="s">
-        <x:v>178</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="K10" s="5">
         <x:v>37.349119163634199</x:v>
@@ -1621,19 +1644,19 @@
     </x:row>
     <x:row r="11" spans="1:12" ht="409.5">
       <x:c r="A11" s="1" t="s">
-        <x:v>188</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F11" s="10">
         <x:v>0</x:v>
@@ -1645,10 +1668,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I11" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="J11" s="12" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K11" s="5">
         <x:v>37.4068936118354</x:v>
@@ -1659,19 +1682,19 @@
     </x:row>
     <x:row r="12" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A12" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F12" s="6">
         <x:v>2</x:v>
@@ -1683,10 +1706,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I12" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="J12" s="5" t="s">
-        <x:v>134</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="K12" s="5">
         <x:v>37.3868626447845</x:v>
@@ -1697,19 +1720,19 @@
     </x:row>
     <x:row r="13" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A13" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F13" s="6">
         <x:v>4</x:v>
@@ -1721,7 +1744,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I13" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="J13" s="5"/>
       <x:c r="K13" s="5">
@@ -1733,19 +1756,19 @@
     </x:row>
     <x:row r="14" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A14" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F14" s="6">
         <x:v>1</x:v>
@@ -1757,7 +1780,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I14" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="J14" s="5"/>
       <x:c r="K14" s="5">
@@ -1769,19 +1792,19 @@
     </x:row>
     <x:row r="15" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A15" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F15" s="6">
         <x:v>3</x:v>
@@ -1793,7 +1816,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I15" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="J15" s="5"/>
       <x:c r="K15" s="5">
@@ -1805,19 +1828,19 @@
     </x:row>
     <x:row r="16" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A16" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F16" s="6">
         <x:v>2</x:v>
@@ -1829,7 +1852,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I16" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="J16" s="5"/>
       <x:c r="K16" s="5">
@@ -1841,19 +1864,19 @@
     </x:row>
     <x:row r="17" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A17" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F17" s="6">
         <x:v>3</x:v>
@@ -1865,7 +1888,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I17" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="J17" s="5"/>
       <x:c r="K17" s="5">
@@ -1877,19 +1900,19 @@
     </x:row>
     <x:row r="18" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A18" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F18" s="6">
         <x:v>2</x:v>
@@ -1901,7 +1924,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I18" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="J18" s="5"/>
       <x:c r="K18" s="5">
@@ -1913,19 +1936,19 @@
     </x:row>
     <x:row r="19" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A19" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F19" s="6">
         <x:v>2</x:v>
@@ -1934,10 +1957,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="H19" s="9" t="s">
-        <x:v>138</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="I19" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="J19" s="5"/>
       <x:c r="K19" s="5">
@@ -1949,19 +1972,19 @@
     </x:row>
     <x:row r="20" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A20" s="1" t="s">
-        <x:v>161</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="F20" s="6">
         <x:v>1</x:v>
@@ -1973,7 +1996,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I20" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="J20" s="5"/>
       <x:c r="K20" s="5">
@@ -1985,19 +2008,19 @@
     </x:row>
     <x:row r="21" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A21" s="1" t="s">
-        <x:v>183</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>149</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F21" s="6">
         <x:v>2</x:v>
@@ -2009,7 +2032,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I21" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="J21" s="5"/>
       <x:c r="K21" s="5">
@@ -2021,34 +2044,34 @@
     </x:row>
     <x:row r="22" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A22" s="13" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="B22" s="13" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="C22" s="13" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="B22" s="13" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="C22" s="13" t="s">
-        <x:v>128</x:v>
-      </x:c>
       <x:c r="D22" s="13" t="s">
-        <x:v>147</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="E22" s="13" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F22" s="14" t="s">
-        <x:v>192</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="G22" s="15" t="s">
-        <x:v>173</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H22" s="3">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I22" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="J22" s="5" t="s">
-        <x:v>90</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K22" s="5">
         <x:v>37.356151021147198</x:v>
@@ -2059,19 +2082,19 @@
     </x:row>
     <x:row r="23" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A23" s="1" t="s">
-        <x:v>174</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>164</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F23" s="6">
         <x:v>2</x:v>
@@ -2083,7 +2106,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I23" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="J23" s="5"/>
       <x:c r="K23" s="5">
@@ -2095,19 +2118,19 @@
     </x:row>
     <x:row r="24" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A24" s="1" t="s">
-        <x:v>185</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>150</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F24" s="6">
         <x:v>2</x:v>
@@ -2119,31 +2142,31 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="I24" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="J24" s="5"/>
-      <x:c r="K24" s="5">
-        <x:v>35.228763193729499</x:v>
-      </x:c>
-      <x:c r="L24" s="5">
-        <x:v>129.15693146248401</x:v>
+      <x:c r="K24" s="20" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="L24" s="20" t="s">
+        <x:v>196</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A25" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>167</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F25" s="6">
         <x:v>2</x:v>
@@ -2155,7 +2178,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I25" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="J25" s="5"/>
       <x:c r="K25" s="5">
@@ -2167,19 +2190,19 @@
     </x:row>
     <x:row r="26" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A26" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F26" s="6">
         <x:v>2</x:v>
@@ -2191,7 +2214,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I26" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="J26" s="5"/>
       <x:c r="K26" s="5">
@@ -2203,19 +2226,19 @@
     </x:row>
     <x:row r="27" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A27" s="1" t="s">
-        <x:v>157</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F27" s="6">
         <x:v>2</x:v>
@@ -2227,7 +2250,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I27" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="J27" s="5"/>
       <x:c r="K27" s="5">
@@ -2239,19 +2262,19 @@
     </x:row>
     <x:row r="28" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A28" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F28" s="6">
         <x:v>3</x:v>
@@ -2263,7 +2286,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I28" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="J28" s="5"/>
       <x:c r="K28" s="5">
@@ -2275,19 +2298,19 @@
     </x:row>
     <x:row r="29" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A29" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>167</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F29" s="6">
         <x:v>2</x:v>
@@ -2299,7 +2322,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I29" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="J29" s="5"/>
       <x:c r="K29" s="5">
@@ -2311,19 +2334,19 @@
     </x:row>
     <x:row r="30" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A30" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>164</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F30" s="6">
         <x:v>1</x:v>
@@ -2335,7 +2358,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I30" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="J30" s="5"/>
       <x:c r="K30" s="5">
@@ -2347,19 +2370,19 @@
     </x:row>
     <x:row r="31" spans="1:12" ht="26.35000000000000142109">
       <x:c r="A31" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>162</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="D31" s="16" t="s">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F31" s="6">
         <x:v>3</x:v>
@@ -2371,7 +2394,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I31" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="J31" s="5"/>
       <x:c r="K31" s="5">
@@ -2383,19 +2406,19 @@
     </x:row>
     <x:row r="32" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A32" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>164</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F32" s="6">
         <x:v>2</x:v>
@@ -2407,7 +2430,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I32" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="J32" s="5"/>
       <x:c r="K32" s="5">
@@ -2419,19 +2442,19 @@
     </x:row>
     <x:row r="33" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A33" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>182</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F33" s="6">
         <x:v>2</x:v>
@@ -2443,7 +2466,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I33" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="J33" s="5"/>
       <x:c r="K33" s="5">
@@ -2455,19 +2478,19 @@
     </x:row>
     <x:row r="34" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A34" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>148</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F34" s="6">
         <x:v>3</x:v>
@@ -2479,7 +2502,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I34" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="J34" s="5"/>
       <x:c r="K34" s="5">
@@ -2491,19 +2514,19 @@
     </x:row>
     <x:row r="35" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A35" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F35" s="6">
         <x:v>2</x:v>
@@ -2515,7 +2538,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I35" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="J35" s="5"/>
       <x:c r="K35" s="5">
@@ -2527,19 +2550,19 @@
     </x:row>
     <x:row r="36" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A36" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F36" s="6">
         <x:v>3</x:v>
@@ -2551,31 +2574,31 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I36" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="J36" s="5"/>
-      <x:c r="K36" s="5">
-        <x:v>33.479625750039901</x:v>
-      </x:c>
-      <x:c r="L36" s="5">
-        <x:v>126.895447088323</x:v>
+      <x:c r="K36" s="20" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="L36" s="20" t="s">
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A37" s="1" t="s">
-        <x:v>156</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>164</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F37" s="6">
         <x:v>2</x:v>
@@ -2587,7 +2610,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I37" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="J37" s="5"/>
       <x:c r="K37" s="5">
@@ -2599,19 +2622,19 @@
     </x:row>
     <x:row r="38" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A38" s="1" t="s">
-        <x:v>171</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F38" s="6">
         <x:v>2</x:v>
@@ -2623,7 +2646,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I38" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="J38" s="5" t="s">
         <x:v>0</x:v>
@@ -2637,19 +2660,19 @@
     </x:row>
     <x:row r="39" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A39" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="F39" s="6">
         <x:v>2</x:v>
@@ -2661,7 +2684,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I39" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="J39" s="5"/>
       <x:c r="K39" s="5">
@@ -2673,19 +2696,19 @@
     </x:row>
     <x:row r="40" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A40" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F40" s="6">
         <x:v>2</x:v>
@@ -2697,7 +2720,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I40" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="J40" s="5"/>
       <x:c r="K40" s="5">
@@ -2709,19 +2732,19 @@
     </x:row>
     <x:row r="41" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A41" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F41" s="6">
         <x:v>2</x:v>
@@ -2733,7 +2756,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I41" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="J41" s="5"/>
       <x:c r="K41" s="5">
@@ -2745,19 +2768,19 @@
     </x:row>
     <x:row r="42" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A42" s="1" t="s">
-        <x:v>184</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>182</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F42" s="6">
         <x:v>2</x:v>
@@ -2769,7 +2792,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I42" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="J42" s="5"/>
       <x:c r="K42" s="5">
@@ -2781,34 +2804,34 @@
     </x:row>
     <x:row r="43" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A43" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F43" s="17" t="s">
-        <x:v>192</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="G43" s="15" t="s">
-        <x:v>132</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="H43" s="3">
         <x:v>3</x:v>
       </x:c>
       <x:c r="I43" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="J43" s="5" t="s">
-        <x:v>90</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K43" s="5">
         <x:v>37.447733087317197</x:v>
@@ -2819,19 +2842,19 @@
     </x:row>
     <x:row r="44" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A44" s="1" t="s">
-        <x:v>170</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F44" s="6">
         <x:v>3</x:v>
@@ -2843,7 +2866,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I44" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="J44" s="5"/>
       <x:c r="K44" s="5">
@@ -2855,19 +2878,19 @@
     </x:row>
     <x:row r="45" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A45" s="1" t="s">
-        <x:v>191</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F45" s="6">
         <x:v>3</x:v>
@@ -2879,7 +2902,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I45" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="J45" s="5"/>
       <x:c r="K45" s="5">
@@ -2891,34 +2914,34 @@
     </x:row>
     <x:row r="46" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A46" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="F46" s="17" t="s">
-        <x:v>192</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="G46" s="15" t="s">
-        <x:v>168</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="H46" s="3">
         <x:v>3</x:v>
       </x:c>
       <x:c r="I46" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="J46" s="5" t="s">
-        <x:v>90</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K46" s="5">
         <x:v>37.3410220277447</x:v>
@@ -2929,19 +2952,19 @@
     </x:row>
     <x:row r="47" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A47" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F47" s="6">
         <x:v>2</x:v>
@@ -2953,7 +2976,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I47" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="J47" s="5"/>
       <x:c r="K47" s="5">
@@ -2965,19 +2988,19 @@
     </x:row>
     <x:row r="48" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A48" s="1" t="s">
-        <x:v>166</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F48" s="6">
         <x:v>3</x:v>
@@ -2989,7 +3012,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="I48" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="J48" s="5"/>
       <x:c r="K48" s="5">
@@ -3001,19 +3024,19 @@
     </x:row>
     <x:row r="49" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A49" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>196</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F49" s="7">
         <x:v>0</x:v>
@@ -3025,10 +3048,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I49" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="J49" s="5" t="s">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="K49" s="5">
         <x:v>37.4360625257819</x:v>
@@ -3039,19 +3062,19 @@
     </x:row>
     <x:row r="50" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A50" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F50" s="6">
         <x:v>1</x:v>
@@ -3063,7 +3086,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I50" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="J50" s="5"/>
       <x:c r="K50" s="5">
@@ -3075,19 +3098,19 @@
     </x:row>
     <x:row r="51" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A51" s="1" t="s">
-        <x:v>163</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>158</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="F51" s="6">
         <x:v>3</x:v>
@@ -3099,7 +3122,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I51" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="J51" s="5"/>
       <x:c r="K51" s="5">
@@ -3111,34 +3134,34 @@
     </x:row>
     <x:row r="52" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A52" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="F52" s="18" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G52" s="19" t="s">
-        <x:v>193</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H52" s="3">
         <x:v>2</x:v>
       </x:c>
       <x:c r="I52" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="J52" s="5" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="K52" s="5">
         <x:v>37.365614337187303</x:v>
@@ -3149,19 +3172,19 @@
     </x:row>
     <x:row r="53" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A53" s="1" t="s">
-        <x:v>181</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F53" s="6">
         <x:v>1</x:v>
@@ -3173,7 +3196,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I53" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="J53" s="5"/>
       <x:c r="K53" s="5">

--- a/data/elementary.xlsx
+++ b/data/elementary.xlsx
@@ -21,19 +21,336 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="208">
   <x:si>
-    <x:t>⊙연성초등학교 학구 중 목감동 1~2통, 3통 4반~6반은 목감중학구 및 안산시 안산중학구와 공동학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보조인력 배치 유/무</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 특수/순회학급수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-364-1700</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-500-0601</x:t>
+    <x:r>
+      <x:t>37.360228</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t>⊙목감초등학교 학구 중 목감동 4통, 6통은 안산중학구와 공동학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 연락처</x:t>
+  </x:si>
+  <x:si>
+    <x:t>37.34</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 학교설립별</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 학교명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>126.72</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정왕초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16/ 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>목감중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정왕중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군자초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군자중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>검바위초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>승지초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장곡중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서해초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소래초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>산현초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군서초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>웃터골초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>진영초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>함현초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>목감초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>진말초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수/순회)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도일초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>조남초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥능곡중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대야초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시화중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥매화중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하중초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시화초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연성중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소래중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21/ 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>은빛초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연성초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2/ 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>포리초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신천초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>생금초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>은계초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>운흥초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16/ 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24/ 12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3학기제</x:t>
+  </x:si>
+  <x:si>
+    <x:t>냉정초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서촌초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장곡초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>송운초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9/ 3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>월포초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>금모래초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3/ 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도창초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥터초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>월곶중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>계수초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-503-1020</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-364-3410</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-0204</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 승지로 110</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7014-4072</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-1683</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(복합특수/시간제/일반)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-2576</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8099-9703</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-364-7903</x:t>
+  </x:si>
+  <x:si>
+    <x:t>복특 6학급/ 시간제 2학급</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-2707</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8032-6504</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 나분들길 44</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-312-3600</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-1553</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8063-2903</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7096-6872</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8063-7873</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-2204</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-412-4300</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8042-2502</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-434-6152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8099-5900</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-2915</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 정왕천로427번길 30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 수인로 3413번길 34</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 대은로 104번길 29-10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 해송십리로 472-30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 정왕대로118번길 27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 수인로3247번길 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 정왕대로 53번길 14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 하중로 209번길 10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 정왕대로 143번길 15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 서울대학로 150-17</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">경기도 시흥시 은행동 663 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 수인로2793번길 6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 신천로 7번길 12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 군서마을로 101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 목감둘레로 109</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 시청로80번길 5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 죽율로 45-42</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 목감둘레로 229-9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 중심상가로 257</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 목감남서로 68</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 큰솔로 7번길 10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 월곶중앙로 18</x:t>
   </x:si>
   <x:si>
     <x:t>⊙도창초등학교 학구 중 매화동 5통, 매화동 20~22통은 시흥매화중학구와 공동학구
@@ -41,61 +358,34 @@
 ⊙도창초등학교 학구 중 과림동 1통(노무저리 제외),  과림동 2통은 광명시 광명중학군과 공동학구</x:t>
   </x:si>
   <x:si>
+    <x:t>⊙연성초등학교 학구 중 목감동 1~2통, 3통 4반~6반은 목감중학구 및 안산시 안산중학구와 공동학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-1108</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-0603</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-363-5904</x:t>
+  </x:si>
+  <x:si>
     <x:t>031-363-3003</x:t>
   </x:si>
   <x:si>
-    <x:t>070-7097-1108</x:t>
+    <x:t>031-8044-1261</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-500-0601</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 포도원로 88</x:t>
   </x:si>
   <x:si>
     <x:t>성인 · 주부 · 어르신</x:t>
   </x:si>
   <x:si>
-    <x:t>경기도 시흥시 포도원로 88</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-0603</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8044-1261</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-363-5904</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8040-6505</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 옥터로 33</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 포도원로 39</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-4878-2804</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 역전로 369</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-503-1538</x:t>
-  </x:si>
-  <x:si>
-    <x:t>계수초등학교 학구 중 계수동은 부천시 소사옥길중학군과 공동학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-317-2701</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-490-8204</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한여울초등학교(복합특수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8085-7004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8042-0700</x:t>
+    <x:t>031-364-1700</x:t>
   </x:si>
   <x:si>
     <x:t>070-7096-7706</x:t>
@@ -108,552 +398,258 @@
     <x:t>070-4648-5770</x:t>
   </x:si>
   <x:si>
+    <x:t>070-7014-8703</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 은행고길 18</x:t>
+  </x:si>
+  <x:si>
     <x:t>031-363-1526</x:t>
   </x:si>
   <x:si>
-    <x:t>070-7014-8703</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 은행고길 18</x:t>
-  </x:si>
-  <x:si>
     <x:t>경기도 시흥시 군자로 539</x:t>
   </x:si>
   <x:si>
-    <x:t>031-8099-5900</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8042-2502</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8063-2903</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-2915</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-2707</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-364-7903</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8032-6504</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8063-7873</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8099-9703</x:t>
-  </x:si>
-  <x:si>
-    <x:t>복특 6학급/ 시간제 2학급</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-2576</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-1553</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 나분들길 44</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-312-3600</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7096-6872</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-2204</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-412-4300</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-434-6152</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-503-1020</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-364-3410</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 승지로 110</x:t>
+    <x:t>031-490-8204</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한여울초등학교(복합특수)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8042-0700</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 옥터로 33</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-4878-2804</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8040-6505</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 포도원로 39</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 역전로 369</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-503-1538</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-317-2701</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8085-7004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 배곧 4로 44-5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 월곶해안로 69</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 군자로465번길 7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 장현능곡로 33</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 배곧4로 94-39</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 대은로 16-29</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 목감초등길 49</x:t>
   </x:si>
   <x:si>
     <x:t>경기도 시흥시 배곧1로 28-25</x:t>
   </x:si>
   <x:si>
-    <x:t>경기도 시흥시 장현능곡로 33</x:t>
+    <x:t>경기도 시흥시 대은로103번길 24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 능곡중앙로 22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 장곡로 70번길 12</x:t>
   </x:si>
   <x:si>
     <x:t>경기도 시흥시 거북섬남로 70</x:t>
   </x:si>
   <x:si>
-    <x:t>경기도 시흥시 장곡로 70번길 12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 대은로103번길 24</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 대은로 16-29</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 월곶해안로 69</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 능곡중앙로 22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-0204</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-1683</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7014-4072</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(복합특수/시간제/일반)</x:t>
+    <x:t>군서미래국제학교(초)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥월곶초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥매화초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수/순회/일반)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥신일초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시화나래초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥은행초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>목감중학구/조남중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧해솔초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧라라초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧누리초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥장현초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한국글로벌중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥능곡초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧라온초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧한울초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥가온초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥도원초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소래중학구/연성중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보조인력 배치 유/무</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 특수/순회학급수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 옥구천동로 433-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 신현로 202번길 31</x:t>
+  </x:si>
+  <x:si>
+    <x:t>특수/순회학급 배치 학생 수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일반학급 배치 학생 수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>계수초등학교 학구 중 계수동은 부천시 소사옥길중학군과 공동학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>위도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공립</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 비고</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 주소</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 호현로 27번길 14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 황고개로 567</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 서울대학로 255</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7096-7801</x:t>
   </x:si>
   <x:si>
     <x:t>031-310-4695</x:t>
   </x:si>
   <x:si>
+    <x:t>031-8042-0004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-0802</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-494-4167</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-2302</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-503-0560</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-1303</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7015-4404</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7096-7772</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 능곡군자로 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-365-8003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7096-6083</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한국글로벌중학구/ 소래중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 매화1로 6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 대골안길 31</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 계수로 203</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7016-3005</x:t>
+  </x:si>
+  <x:si>
     <x:t>경기도 시흥시 역전로 455</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8042-0004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 능곡군자로 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-0802</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-503-0560</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-494-4167</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 대골안길 31</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-2302</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 매화1로 6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-1303</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7015-4404</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7096-6083</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7096-7772</x:t>
-  </x:si>
-  <x:si>
-    <x:t>군서미래국제학교(초)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥신일초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧누리초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥매화초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시화나래초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>목감중학구/조남중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧해솔초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥은행초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥월곶초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧라라초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수/순회/일반)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥가온초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소래중학구/연성중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥장현초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한국글로벌중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥능곡초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧한울초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧라온초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥도원초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 군자로465번길 7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 목감초등길 49</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 배곧 4로 44-5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 목감남서로 68</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 신천로 7번길 12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 수인로2793번길 6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 목감둘레로 109</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 군서마을로 101</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 죽율로 45-42</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 중심상가로 257</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 시청로80번길 5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 큰솔로 7번길 10</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">경기도 시흥시 은행동 663 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 월곶중앙로 18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 호현로 27번길 14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-365-8003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7016-3005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 계수로 203</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한국글로벌중학구/ 소래중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7096-7801</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 서울대학로 255</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 목감둘레로 229-9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 황고개로 567</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 배곧4로 94-39</x:t>
-  </x:si>
-  <x:si>
-    <x:t>검바위초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정왕초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장곡중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>서해초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정왕중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>군자중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>승지초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>목감중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16/ 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>군자초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>⊙목감초등학교 학구 중 목감동 4통, 6통은 안산중학구와 공동학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>위도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공립</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 정왕천로427번길 30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 서울대학로 150-17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 정왕대로 143번길 15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 해송십리로 472-30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 하중로 209번길 10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 수인로3247번길 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 수인로 3413번길 34</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 정왕대로 53번길 14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 대은로 104번길 29-10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 정왕대로118번길 27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 옥구천동로 433-25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 신현로 202번길 31</x:t>
-  </x:si>
-  <x:si>
-    <x:t>조남초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>목감초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>운흥초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시화중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>신천초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시화초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연성중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도일초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대야초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>생금초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥매화중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하중초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소래중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>은계초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>진말초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥능곡중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21/ 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2/ 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>은빛초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연성초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>포리초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16/ 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소래초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>진영초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>산현초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수/순회)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>군서초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>웃터골초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>함현초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>월곶중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>서촌초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>월포초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>송운초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>계수초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9/ 3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도창초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>금모래초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>냉정초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장곡초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3/ 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24/ 12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥터초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3학기제</x:t>
   </x:si>
   <x:si>
     <x:r>
       <x:t>126.730065</x:t>
     </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 비고</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 주소</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 학구</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:t>37.360228,</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:t>126.72</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:t>37.34</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 학교설립별</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 연락처</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 학교명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>특수/순회학급 배치 학생 수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일반학급 배치 학생 수</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -700,53 +696,22 @@
       <x:sz val="11"/>
       <x:color rgb="ff000000"/>
     </x:font>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:font hs:extension="1">
-          <x:name val="Arial"/>
-          <x:sz val="10"/>
-          <x:color rgb="ff000000"/>
-          <hs:size val="100"/>
-          <hs:ratio val="100"/>
-          <hs:spacing val="0"/>
-          <hs:offset val="0"/>
-        </x:font>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:font>
-          <x:name val="Arial"/>
-          <x:sz val="10"/>
-          <x:color rgb="ff000000"/>
-        </x:font>
-      </mc:Fallback>
-    </mc:AlternateContent>
+    <x:font>
+      <x:name val="Arial"/>
+      <x:sz val="10"/>
+      <x:color rgb="ff000000"/>
+    </x:font>
     <x:font>
       <x:name val="돋움"/>
       <x:sz val="11"/>
       <x:color rgb="ff000000"/>
     </x:font>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:font hs:extension="1">
-          <x:name val="맑은 고딕"/>
-          <x:sz val="11"/>
-          <x:color rgb="ff000000"/>
-          <x:b val="1"/>
-          <hs:size val="100"/>
-          <hs:ratio val="100"/>
-          <hs:spacing val="0"/>
-          <hs:offset val="0"/>
-        </x:font>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:font>
-          <x:name val="맑은 고딕"/>
-          <x:sz val="11"/>
-          <x:color rgb="ff000000"/>
-          <x:b val="1"/>
-        </x:font>
-      </mc:Fallback>
-    </mc:AlternateContent>
+    <x:font>
+      <x:name val="맑은 고딕"/>
+      <x:sz val="11"/>
+      <x:color rgb="ff000000"/>
+      <x:b val="1"/>
+    </x:font>
   </x:fonts>
   <x:fills count="2">
     <x:fill>
@@ -1278,57 +1243,57 @@
   <x:sheetData>
     <x:row r="1" spans="1:12">
       <x:c r="A1" t="s">
-        <x:v>205</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B1" t="s">
-        <x:v>203</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C1" t="s">
-        <x:v>199</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="D1" t="s">
-        <x:v>198</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="E1" t="s">
-        <x:v>204</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F1" t="s">
-        <x:v>2</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="G1" t="s">
-        <x:v>206</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="H1" t="s">
-        <x:v>207</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="I1" t="s">
-        <x:v>1</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="J1" t="s">
-        <x:v>197</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="K1" t="s">
-        <x:v>135</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="L1" t="s">
-        <x:v>134</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A2" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B2" s="1" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="D2" s="1" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="E2" s="1" t="s">
         <x:v>136</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="E2" s="1" t="s">
-        <x:v>18</x:v>
       </x:c>
       <x:c r="F2" s="2">
         <x:v>3</x:v>
@@ -1340,7 +1305,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I2" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="J2" s="5"/>
       <x:c r="K2" s="5">
@@ -1352,19 +1317,19 @@
     </x:row>
     <x:row r="3" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A3" s="1" t="s">
-        <x:v>185</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="F3" s="6">
         <x:v>1</x:v>
@@ -1376,10 +1341,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I3" s="4" t="s">
-        <x:v>137</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="J3" s="5" t="s">
-        <x:v>19</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="K3" s="5">
         <x:v>37.453471946211501</x:v>
@@ -1390,19 +1355,19 @@
     </x:row>
     <x:row r="4" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A4" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="F4" s="7">
         <x:v>0</x:v>
@@ -1414,7 +1379,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I4" s="4" t="s">
-        <x:v>137</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="J4" s="5"/>
       <x:c r="K4" s="5">
@@ -1426,19 +1391,19 @@
     </x:row>
     <x:row r="5" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A5" s="1" t="s">
-        <x:v>178</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="F5" s="6">
         <x:v>3</x:v>
@@ -1450,7 +1415,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I5" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="J5" s="5"/>
       <x:c r="K5" s="5">
@@ -1462,19 +1427,19 @@
     </x:row>
     <x:row r="6" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A6" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="F6" s="6">
         <x:v>4</x:v>
@@ -1486,7 +1451,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I6" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="J6" s="5"/>
       <x:c r="K6" s="5">
@@ -1498,19 +1463,19 @@
     </x:row>
     <x:row r="7" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A7" s="1" t="s">
-        <x:v>188</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="F7" s="6">
         <x:v>2</x:v>
@@ -1522,7 +1487,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I7" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="J7" s="5"/>
       <x:c r="K7" s="5">
@@ -1534,19 +1499,19 @@
     </x:row>
     <x:row r="8" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A8" s="1" t="s">
-        <x:v>189</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="F8" s="6">
         <x:v>3</x:v>
@@ -1558,7 +1523,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I8" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="J8" s="5"/>
       <x:c r="K8" s="5">
@@ -1570,19 +1535,19 @@
     </x:row>
     <x:row r="9" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A9" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="F9" s="6">
         <x:v>3</x:v>
@@ -1594,7 +1559,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I9" s="4" t="s">
-        <x:v>137</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="J9" s="5"/>
       <x:c r="K9" s="5">
@@ -1606,34 +1571,34 @@
     </x:row>
     <x:row r="10" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A10" s="1" t="s">
-        <x:v>158</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="F10" s="8" t="s">
-        <x:v>168</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G10" s="9" t="s">
-        <x:v>186</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H10" s="3">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I10" s="4" t="s">
-        <x:v>137</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="J10" s="5" t="s">
-        <x:v>177</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="K10" s="5">
         <x:v>37.349119163634199</x:v>
@@ -1644,19 +1609,19 @@
     </x:row>
     <x:row r="11" spans="1:12" ht="409.5">
       <x:c r="A11" s="1" t="s">
-        <x:v>187</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="F11" s="10">
         <x:v>0</x:v>
@@ -1668,10 +1633,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I11" s="4" t="s">
-        <x:v>137</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="J11" s="12" t="s">
-        <x:v>5</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="K11" s="5">
         <x:v>37.4068936118354</x:v>
@@ -1682,19 +1647,19 @@
     </x:row>
     <x:row r="12" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A12" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F12" s="6">
         <x:v>2</x:v>
@@ -1706,10 +1671,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I12" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="J12" s="5" t="s">
-        <x:v>133</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K12" s="5">
         <x:v>37.3868626447845</x:v>
@@ -1720,19 +1685,19 @@
     </x:row>
     <x:row r="13" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A13" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F13" s="6">
         <x:v>4</x:v>
@@ -1744,7 +1709,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I13" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="J13" s="5"/>
       <x:c r="K13" s="5">
@@ -1756,19 +1721,19 @@
     </x:row>
     <x:row r="14" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A14" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F14" s="6">
         <x:v>1</x:v>
@@ -1780,7 +1745,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I14" s="4" t="s">
-        <x:v>137</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="J14" s="5"/>
       <x:c r="K14" s="5">
@@ -1792,19 +1757,19 @@
     </x:row>
     <x:row r="15" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A15" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="F15" s="6">
         <x:v>3</x:v>
@@ -1816,7 +1781,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I15" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="J15" s="5"/>
       <x:c r="K15" s="5">
@@ -1828,19 +1793,19 @@
     </x:row>
     <x:row r="16" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A16" s="1" t="s">
-        <x:v>193</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F16" s="6">
         <x:v>2</x:v>
@@ -1852,7 +1817,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I16" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="J16" s="5"/>
       <x:c r="K16" s="5">
@@ -1864,19 +1829,19 @@
     </x:row>
     <x:row r="17" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A17" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="F17" s="6">
         <x:v>3</x:v>
@@ -1888,7 +1853,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I17" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="J17" s="5"/>
       <x:c r="K17" s="5">
@@ -1900,19 +1865,19 @@
     </x:row>
     <x:row r="18" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A18" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="F18" s="6">
         <x:v>2</x:v>
@@ -1924,7 +1889,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I18" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="J18" s="5"/>
       <x:c r="K18" s="5">
@@ -1936,19 +1901,19 @@
     </x:row>
     <x:row r="19" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A19" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="F19" s="6">
         <x:v>2</x:v>
@@ -1957,10 +1922,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="H19" s="9" t="s">
-        <x:v>137</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="I19" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="J19" s="5"/>
       <x:c r="K19" s="5">
@@ -1972,19 +1937,19 @@
     </x:row>
     <x:row r="20" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A20" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="F20" s="6">
         <x:v>1</x:v>
@@ -1996,7 +1961,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I20" s="4" t="s">
-        <x:v>137</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="J20" s="5"/>
       <x:c r="K20" s="5">
@@ -2008,19 +1973,19 @@
     </x:row>
     <x:row r="21" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A21" s="1" t="s">
-        <x:v>182</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>148</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F21" s="6">
         <x:v>2</x:v>
@@ -2032,7 +1997,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I21" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="J21" s="5"/>
       <x:c r="K21" s="5">
@@ -2044,34 +2009,34 @@
     </x:row>
     <x:row r="22" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A22" s="13" t="s">
-        <x:v>126</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B22" s="13" t="s">
-        <x:v>136</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C22" s="13" t="s">
-        <x:v>127</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D22" s="13" t="s">
-        <x:v>146</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E22" s="13" t="s">
-        <x:v>49</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F22" s="14" t="s">
-        <x:v>191</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G22" s="15" t="s">
-        <x:v>172</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="H22" s="3">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I22" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="J22" s="5" t="s">
-        <x:v>89</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="K22" s="5">
         <x:v>37.356151021147198</x:v>
@@ -2082,19 +2047,19 @@
     </x:row>
     <x:row r="23" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A23" s="1" t="s">
-        <x:v>173</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>163</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F23" s="6">
         <x:v>2</x:v>
@@ -2106,7 +2071,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I23" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="J23" s="5"/>
       <x:c r="K23" s="5">
@@ -2118,19 +2083,19 @@
     </x:row>
     <x:row r="24" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A24" s="1" t="s">
-        <x:v>184</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>149</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="F24" s="6">
         <x:v>2</x:v>
@@ -2142,31 +2107,31 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="I24" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="J24" s="5"/>
       <x:c r="K24" s="20" t="s">
-        <x:v>200</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L24" s="20" t="s">
-        <x:v>196</x:v>
+        <x:v>207</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A25" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>166</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="F25" s="6">
         <x:v>2</x:v>
@@ -2178,7 +2143,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I25" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="J25" s="5"/>
       <x:c r="K25" s="5">
@@ -2190,19 +2155,19 @@
     </x:row>
     <x:row r="26" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A26" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F26" s="6">
         <x:v>2</x:v>
@@ -2214,7 +2179,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I26" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="J26" s="5"/>
       <x:c r="K26" s="5">
@@ -2226,19 +2191,19 @@
     </x:row>
     <x:row r="27" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A27" s="1" t="s">
-        <x:v>156</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="F27" s="6">
         <x:v>2</x:v>
@@ -2250,7 +2215,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I27" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="J27" s="5"/>
       <x:c r="K27" s="5">
@@ -2262,19 +2227,19 @@
     </x:row>
     <x:row r="28" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A28" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="F28" s="6">
         <x:v>3</x:v>
@@ -2286,7 +2251,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I28" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="J28" s="5"/>
       <x:c r="K28" s="5">
@@ -2298,19 +2263,19 @@
     </x:row>
     <x:row r="29" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A29" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>166</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F29" s="6">
         <x:v>2</x:v>
@@ -2322,7 +2287,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I29" s="4" t="s">
-        <x:v>137</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="J29" s="5"/>
       <x:c r="K29" s="5">
@@ -2334,19 +2299,19 @@
     </x:row>
     <x:row r="30" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A30" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>163</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="F30" s="6">
         <x:v>1</x:v>
@@ -2358,7 +2323,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I30" s="4" t="s">
-        <x:v>137</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="J30" s="5"/>
       <x:c r="K30" s="5">
@@ -2370,19 +2335,19 @@
     </x:row>
     <x:row r="31" spans="1:12" ht="26.35000000000000142109">
       <x:c r="A31" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>161</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D31" s="16" t="s">
-        <x:v>74</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="F31" s="6">
         <x:v>3</x:v>
@@ -2394,7 +2359,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I31" s="4" t="s">
-        <x:v>137</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="J31" s="5"/>
       <x:c r="K31" s="5">
@@ -2406,19 +2371,19 @@
     </x:row>
     <x:row r="32" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A32" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>163</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="F32" s="6">
         <x:v>2</x:v>
@@ -2430,7 +2395,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I32" s="4" t="s">
-        <x:v>137</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="J32" s="5"/>
       <x:c r="K32" s="5">
@@ -2442,19 +2407,19 @@
     </x:row>
     <x:row r="33" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A33" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>181</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F33" s="6">
         <x:v>2</x:v>
@@ -2466,7 +2431,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I33" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="J33" s="5"/>
       <x:c r="K33" s="5">
@@ -2478,19 +2443,19 @@
     </x:row>
     <x:row r="34" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A34" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>147</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F34" s="6">
         <x:v>3</x:v>
@@ -2502,7 +2467,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I34" s="4" t="s">
-        <x:v>137</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="J34" s="5"/>
       <x:c r="K34" s="5">
@@ -2514,19 +2479,19 @@
     </x:row>
     <x:row r="35" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A35" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="F35" s="6">
         <x:v>2</x:v>
@@ -2538,7 +2503,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I35" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="J35" s="5"/>
       <x:c r="K35" s="5">
@@ -2550,19 +2515,19 @@
     </x:row>
     <x:row r="36" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A36" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="F36" s="6">
         <x:v>3</x:v>
@@ -2574,31 +2539,31 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I36" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="J36" s="5"/>
       <x:c r="K36" s="20" t="s">
-        <x:v>202</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L36" s="20" t="s">
-        <x:v>201</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A37" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>163</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="F37" s="6">
         <x:v>2</x:v>
@@ -2610,7 +2575,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I37" s="4" t="s">
-        <x:v>137</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="J37" s="5"/>
       <x:c r="K37" s="5">
@@ -2622,19 +2587,19 @@
     </x:row>
     <x:row r="38" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A38" s="1" t="s">
-        <x:v>170</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="F38" s="6">
         <x:v>2</x:v>
@@ -2646,10 +2611,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I38" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="J38" s="5" t="s">
-        <x:v>0</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="K38" s="5">
         <x:v>37.387563889027803</x:v>
@@ -2660,19 +2625,19 @@
     </x:row>
     <x:row r="39" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A39" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="F39" s="6">
         <x:v>2</x:v>
@@ -2684,7 +2649,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I39" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="J39" s="5"/>
       <x:c r="K39" s="5">
@@ -2696,19 +2661,19 @@
     </x:row>
     <x:row r="40" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A40" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="F40" s="6">
         <x:v>2</x:v>
@@ -2720,7 +2685,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I40" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="J40" s="5"/>
       <x:c r="K40" s="5">
@@ -2732,19 +2697,19 @@
     </x:row>
     <x:row r="41" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A41" s="1" t="s">
-        <x:v>179</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="F41" s="6">
         <x:v>2</x:v>
@@ -2756,7 +2721,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I41" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="J41" s="5"/>
       <x:c r="K41" s="5">
@@ -2768,19 +2733,19 @@
     </x:row>
     <x:row r="42" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A42" s="1" t="s">
-        <x:v>183</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>181</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F42" s="6">
         <x:v>2</x:v>
@@ -2792,7 +2757,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I42" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="J42" s="5"/>
       <x:c r="K42" s="5">
@@ -2804,34 +2769,34 @@
     </x:row>
     <x:row r="43" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A43" s="1" t="s">
-        <x:v>164</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="E43" s="1" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="F43" s="17" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="E43" s="1" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="F43" s="17" t="s">
-        <x:v>191</x:v>
-      </x:c>
       <x:c r="G43" s="15" t="s">
-        <x:v>131</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H43" s="3">
         <x:v>3</x:v>
       </x:c>
       <x:c r="I43" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="J43" s="5" t="s">
-        <x:v>89</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="K43" s="5">
         <x:v>37.447733087317197</x:v>
@@ -2842,19 +2807,19 @@
     </x:row>
     <x:row r="44" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A44" s="1" t="s">
-        <x:v>169</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="F44" s="6">
         <x:v>3</x:v>
@@ -2866,7 +2831,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I44" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="J44" s="5"/>
       <x:c r="K44" s="5">
@@ -2878,19 +2843,19 @@
     </x:row>
     <x:row r="45" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A45" s="1" t="s">
-        <x:v>190</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="F45" s="6">
         <x:v>3</x:v>
@@ -2902,7 +2867,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I45" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="J45" s="5"/>
       <x:c r="K45" s="5">
@@ -2914,34 +2879,34 @@
     </x:row>
     <x:row r="46" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A46" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="F46" s="17" t="s">
-        <x:v>191</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G46" s="15" t="s">
-        <x:v>167</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H46" s="3">
         <x:v>3</x:v>
       </x:c>
       <x:c r="I46" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="J46" s="5" t="s">
-        <x:v>89</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="K46" s="5">
         <x:v>37.3410220277447</x:v>
@@ -2952,19 +2917,19 @@
     </x:row>
     <x:row r="47" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A47" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="F47" s="6">
         <x:v>2</x:v>
@@ -2976,7 +2941,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I47" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="J47" s="5"/>
       <x:c r="K47" s="5">
@@ -2988,19 +2953,19 @@
     </x:row>
     <x:row r="48" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A48" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="F48" s="6">
         <x:v>3</x:v>
@@ -3012,7 +2977,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="I48" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="J48" s="5"/>
       <x:c r="K48" s="5">
@@ -3024,19 +2989,19 @@
     </x:row>
     <x:row r="49" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A49" s="1" t="s">
-        <x:v>174</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F49" s="7">
         <x:v>0</x:v>
@@ -3048,10 +3013,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I49" s="4" t="s">
-        <x:v>137</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="J49" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="K49" s="5">
         <x:v>37.4360625257819</x:v>
@@ -3062,19 +3027,19 @@
     </x:row>
     <x:row r="50" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A50" s="1" t="s">
-        <x:v>171</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>150</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F50" s="6">
         <x:v>1</x:v>
@@ -3086,7 +3051,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I50" s="4" t="s">
-        <x:v>137</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="J50" s="5"/>
       <x:c r="K50" s="5">
@@ -3098,19 +3063,19 @@
     </x:row>
     <x:row r="51" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A51" s="1" t="s">
-        <x:v>162</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>157</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="F51" s="6">
         <x:v>3</x:v>
@@ -3122,7 +3087,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I51" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="J51" s="5"/>
       <x:c r="K51" s="5">
@@ -3134,34 +3099,34 @@
     </x:row>
     <x:row r="52" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A52" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="F52" s="18" t="s">
-        <x:v>41</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="G52" s="19" t="s">
-        <x:v>192</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H52" s="3">
         <x:v>2</x:v>
       </x:c>
       <x:c r="I52" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="J52" s="5" t="s">
-        <x:v>64</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="K52" s="5">
         <x:v>37.365614337187303</x:v>
@@ -3172,19 +3137,19 @@
     </x:row>
     <x:row r="53" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A53" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="F53" s="6">
         <x:v>1</x:v>
@@ -3196,7 +3161,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I53" s="4" t="s">
-        <x:v>137</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="J53" s="5"/>
       <x:c r="K53" s="5">

--- a/data/elementary.xlsx
+++ b/data/elementary.xlsx
@@ -19,338 +19,36 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="208">
-  <x:si>
-    <x:r>
-      <x:t>37.360228</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t>⊙목감초등학교 학구 중 목감동 4통, 6통은 안산중학구와 공동학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 연락처</x:t>
-  </x:si>
-  <x:si>
-    <x:t>37.34</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 학교설립별</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 학교명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>126.72</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정왕초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16/ 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>목감중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정왕중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>군자초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>군자중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>검바위초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>승지초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장곡중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>서해초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소래초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>산현초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>군서초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>웃터골초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>진영초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>함현초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>목감초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>진말초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수/순회)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도일초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>조남초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥능곡중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대야초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시화중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥매화중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하중초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시화초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연성중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소래중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21/ 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>은빛초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연성초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2/ 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>포리초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>신천초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>생금초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>은계초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>운흥초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16/ 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24/ 12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3학기제</x:t>
-  </x:si>
-  <x:si>
-    <x:t>냉정초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>서촌초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장곡초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>송운초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9/ 3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>월포초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>금모래초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3/ 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도창초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥터초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>월곶중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>계수초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-503-1020</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-364-3410</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-0204</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 승지로 110</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7014-4072</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-1683</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(복합특수/시간제/일반)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-2576</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8099-9703</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-364-7903</x:t>
-  </x:si>
-  <x:si>
-    <x:t>복특 6학급/ 시간제 2학급</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-2707</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8032-6504</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 나분들길 44</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-312-3600</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-1553</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8063-2903</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7096-6872</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8063-7873</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-2204</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-412-4300</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8042-2502</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-434-6152</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8099-5900</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-2915</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 정왕천로427번길 30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 수인로 3413번길 34</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 대은로 104번길 29-10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 해송십리로 472-30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 정왕대로118번길 27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 수인로3247번길 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 정왕대로 53번길 14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 하중로 209번길 10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 정왕대로 143번길 15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 서울대학로 150-17</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">경기도 시흥시 은행동 663 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 수인로2793번길 6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 신천로 7번길 12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 군서마을로 101</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 목감둘레로 109</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 시청로80번길 5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 죽율로 45-42</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 목감둘레로 229-9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 중심상가로 257</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 목감남서로 68</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 큰솔로 7번길 10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 월곶중앙로 18</x:t>
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="206">
+  <x:si>
+    <x:t>위도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경도</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 주소</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 비고</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공립</x:t>
+  </x:si>
+  <x:si>
+    <x:t>계수초등학교 학구 중 계수동은 부천시 소사옥길중학군과 공동학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 능곡중앙로 22</x:t>
   </x:si>
   <x:si>
     <x:t>⊙도창초등학교 학구 중 매화동 5통, 매화동 20~22통은 시흥매화중학구와 공동학구
@@ -361,28 +59,472 @@
     <x:t>⊙연성초등학교 학구 중 목감동 1~2통, 3통 4반~6반은 목감중학구 및 안산시 안산중학구와 공동학구</x:t>
   </x:si>
   <x:si>
+    <x:t>배곧라라초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧누리초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥매화초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한국글로벌중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥능곡초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥은행초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥장현초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧라온초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥신일초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군서미래국제학교(초)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>목감중학구/조남중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수/순회/일반)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧해솔초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시화나래초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥월곶초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소래중학구/연성중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 특수/순회학급수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧한울초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥가온초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보조인력 배치 유/무</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥도원초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>126.730065</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 월곶중앙로 18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 배곧 4로 44-5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 월곶해안로 69</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 장현능곡로 33</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 군자로465번길 7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 목감남서로 68</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 큰솔로 7번길 10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 서울대학로 255</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 목감둘레로 229-9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 죽율로 45-42</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 중심상가로 257</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 서울대학로 150-17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 정왕대로 143번길 15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 해송십리로 472-30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 수인로 3413번길 34</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 옥구천동로 433-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 신현로 202번길 31</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 정왕천로427번길 30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 대은로 104번길 29-10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 수인로3247번길 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 정왕대로118번길 27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 하중로 209번길 10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 정왕대로 53번길 14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정왕초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>목감중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정왕중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 연락처</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 학교설립별</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 학교명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군자중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16/ 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군자초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>검바위초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>승지초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장곡중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소래초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서해초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>산현초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군서초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>웃터골초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>진영초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>함현초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>목감초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>포리초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신천초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도일초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>조남초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥매화중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>은빛초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시화중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시화초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하중초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소래중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수/순회)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥능곡중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연성중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>진말초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연성초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2/ 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대야초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21/ 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>월곶중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>월포초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서촌초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>생금초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장곡초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도창초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥터초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>은계초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>냉정초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24/ 12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9/ 3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>금모래초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3학기제</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3/ 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16/ 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>계수초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>운흥초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>송운초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>⊙목감초등학교 학구 중 목감동 4통, 6통은 안산중학구와 공동학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>37.360228</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 배곧1로 28-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 대은로103번길 24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7096-7772</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-365-8003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한국글로벌중학구/ 소래중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 계수로 203</x:t>
+  </x:si>
+  <x:si>
+    <x:t>특수/순회학급 배치 학생 수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일반학급 배치 학생 수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-310-4695</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7096-7801</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8042-0004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-503-0560</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-494-4167</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-1303</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 능곡군자로 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7096-6083</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7015-4404</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 매화1로 6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-2302</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 대골안길 31</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-0802</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7016-3005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 역전로 455</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-503-1020</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-0204</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-1683</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7014-4072</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-364-3410</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 승지로 110</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(복합특수/시간제/일반)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8099-9703</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-364-7903</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-2576</x:t>
+  </x:si>
+  <x:si>
+    <x:t>복특 6학급/ 시간제 2학급</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-312-3600</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-2915</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 나분들길 44</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-2204</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8099-5900</x:t>
+  </x:si>
+  <x:si>
     <x:t>070-7097-1108</x:t>
   </x:si>
   <x:si>
+    <x:t>031-8063-7873</x:t>
+  </x:si>
+  <x:si>
     <x:t>070-7097-0603</x:t>
   </x:si>
   <x:si>
+    <x:t>031-434-6152</x:t>
+  </x:si>
+  <x:si>
     <x:t>031-363-5904</x:t>
   </x:si>
   <x:si>
     <x:t>031-363-3003</x:t>
   </x:si>
   <x:si>
-    <x:t>031-8044-1261</x:t>
+    <x:t>031-8032-6504</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7096-6872</x:t>
   </x:si>
   <x:si>
     <x:t>031-500-0601</x:t>
   </x:si>
   <x:si>
+    <x:t>031-8042-2502</x:t>
+  </x:si>
+  <x:si>
     <x:t>경기도 시흥시 포도원로 88</x:t>
-  </x:si>
-  <x:si>
-    <x:t>성인 · 주부 · 어르신</x:t>
   </x:si>
   <x:si>
     <x:t>031-364-1700</x:t>
@@ -401,6 +543,18 @@
     <x:t>070-7014-8703</x:t>
   </x:si>
   <x:si>
+    <x:t>031-412-4300</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8044-1261</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-1553</x:t>
+  </x:si>
+  <x:si>
+    <x:t>성인 · 주부 · 어르신</x:t>
+  </x:si>
+  <x:si>
     <x:t>경기도 시흥시 은행고길 18</x:t>
   </x:si>
   <x:si>
@@ -410,246 +564,82 @@
     <x:t>경기도 시흥시 군자로 539</x:t>
   </x:si>
   <x:si>
+    <x:t>070-7097-2707</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8063-2903</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-4878-2804</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8085-7004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8042-0700</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8040-6505</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한여울초등학교(복합특수)</x:t>
+  </x:si>
+  <x:si>
     <x:t>031-490-8204</x:t>
   </x:si>
   <x:si>
-    <x:t>한여울초등학교(복합특수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8042-0700</x:t>
+    <x:t>경기도 시흥시 포도원로 39</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 역전로 369</x:t>
   </x:si>
   <x:si>
     <x:t>경기도 시흥시 옥터로 33</x:t>
   </x:si>
   <x:si>
-    <x:t>070-4878-2804</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8040-6505</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 포도원로 39</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 역전로 369</x:t>
-  </x:si>
-  <x:si>
     <x:t>031-503-1538</x:t>
   </x:si>
   <x:si>
     <x:t>031-317-2701</x:t>
   </x:si>
   <x:si>
-    <x:t>031-8085-7004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 배곧 4로 44-5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 월곶해안로 69</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 군자로465번길 7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 장현능곡로 33</x:t>
+    <x:t>경기도 시흥시 목감초등길 49</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 대은로 16-29</x:t>
   </x:si>
   <x:si>
     <x:t>경기도 시흥시 배곧4로 94-39</x:t>
   </x:si>
   <x:si>
-    <x:t>경기도 시흥시 대은로 16-29</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 목감초등길 49</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 배곧1로 28-25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 대은로103번길 24</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 능곡중앙로 22</x:t>
+    <x:t>경기도 시흥시 거북섬남로 70</x:t>
   </x:si>
   <x:si>
     <x:t>경기도 시흥시 장곡로 70번길 12</x:t>
   </x:si>
   <x:si>
-    <x:t>경기도 시흥시 거북섬남로 70</x:t>
-  </x:si>
-  <x:si>
-    <x:t>군서미래국제학교(초)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥월곶초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥매화초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수/순회/일반)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥신일초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시화나래초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥은행초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>목감중학구/조남중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧해솔초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧라라초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧누리초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥장현초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한국글로벌중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥능곡초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧라온초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧한울초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥가온초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥도원초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소래중학구/연성중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보조인력 배치 유/무</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 특수/순회학급수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 옥구천동로 433-25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 신현로 202번길 31</x:t>
-  </x:si>
-  <x:si>
-    <x:t>특수/순회학급 배치 학생 수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일반학급 배치 학생 수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>계수초등학교 학구 중 계수동은 부천시 소사옥길중학군과 공동학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>위도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공립</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 비고</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 주소</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경도</x:t>
+    <x:t>경기도 시흥시 황고개로 567</x:t>
   </x:si>
   <x:si>
     <x:t>경기도 시흥시 호현로 27번길 14</x:t>
   </x:si>
   <x:si>
-    <x:t>경기도 시흥시 황고개로 567</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 서울대학로 255</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7096-7801</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-310-4695</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8042-0004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-0802</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-494-4167</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-2302</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-503-0560</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-1303</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7015-4404</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7096-7772</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 능곡군자로 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-365-8003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7096-6083</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한국글로벌중학구/ 소래중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 매화1로 6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 대골안길 31</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 계수로 203</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7016-3005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 역전로 455</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:t>126.730065</x:t>
-    </x:r>
+    <x:t>경기도 시흥시 신천로 7번길 12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 시청로80번길 5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 군서마을로 101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 목감둘레로 109</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 수인로2793번길 6</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">경기도 시흥시 은행동 663 </x:t>
   </x:si>
 </x:sst>
 </file>
@@ -696,22 +686,53 @@
       <x:sz val="11"/>
       <x:color rgb="ff000000"/>
     </x:font>
-    <x:font>
-      <x:name val="Arial"/>
-      <x:sz val="10"/>
-      <x:color rgb="ff000000"/>
-    </x:font>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:font hs:extension="1">
+          <x:name val="Arial"/>
+          <x:sz val="10"/>
+          <x:color rgb="ff000000"/>
+          <hs:size val="100"/>
+          <hs:ratio val="100"/>
+          <hs:spacing val="0"/>
+          <hs:offset val="0"/>
+        </x:font>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:font>
+          <x:name val="Arial"/>
+          <x:sz val="10"/>
+          <x:color rgb="ff000000"/>
+        </x:font>
+      </mc:Fallback>
+    </mc:AlternateContent>
     <x:font>
       <x:name val="돋움"/>
       <x:sz val="11"/>
       <x:color rgb="ff000000"/>
     </x:font>
-    <x:font>
-      <x:name val="맑은 고딕"/>
-      <x:sz val="11"/>
-      <x:color rgb="ff000000"/>
-      <x:b val="1"/>
-    </x:font>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:font hs:extension="1">
+          <x:name val="맑은 고딕"/>
+          <x:sz val="11"/>
+          <x:color rgb="ff000000"/>
+          <x:b val="1"/>
+          <hs:size val="100"/>
+          <hs:ratio val="100"/>
+          <hs:spacing val="0"/>
+          <hs:offset val="0"/>
+        </x:font>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:font>
+          <x:name val="맑은 고딕"/>
+          <x:sz val="11"/>
+          <x:color rgb="ff000000"/>
+          <x:b val="1"/>
+        </x:font>
+      </mc:Fallback>
+    </mc:AlternateContent>
   </x:fonts>
   <x:fills count="2">
     <x:fill>
@@ -1243,57 +1264,57 @@
   <x:sheetData>
     <x:row r="1" spans="1:12">
       <x:c r="A1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C1" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D1" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E1" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="F1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G1" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="H1" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="I1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="J1" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B1" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C1" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="D1" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="E1" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F1" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="G1" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="H1" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="I1" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="J1" t="s">
-        <x:v>181</x:v>
-      </x:c>
       <x:c r="K1" t="s">
-        <x:v>178</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L1" t="s">
-        <x:v>184</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A2" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="F2" s="2">
         <x:v>3</x:v>
@@ -1305,7 +1326,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I2" s="4" t="s">
-        <x:v>177</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="J2" s="5"/>
       <x:c r="K2" s="5">
@@ -1317,19 +1338,19 @@
     </x:row>
     <x:row r="3" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A3" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>163</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>204</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="F3" s="6">
         <x:v>1</x:v>
@@ -1341,10 +1362,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I3" s="4" t="s">
-        <x:v>179</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J3" s="5" t="s">
-        <x:v>176</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="K3" s="5">
         <x:v>37.453471946211501</x:v>
@@ -1355,19 +1376,19 @@
     </x:row>
     <x:row r="4" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A4" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>179</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="F4" s="7">
         <x:v>0</x:v>
@@ -1379,7 +1400,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I4" s="4" t="s">
-        <x:v>179</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J4" s="5"/>
       <x:c r="K4" s="5">
@@ -1391,19 +1412,19 @@
     </x:row>
     <x:row r="5" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A5" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="F5" s="6">
         <x:v>3</x:v>
@@ -1415,7 +1436,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I5" s="4" t="s">
-        <x:v>177</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="J5" s="5"/>
       <x:c r="K5" s="5">
@@ -1427,19 +1448,19 @@
     </x:row>
     <x:row r="6" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A6" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="F6" s="6">
         <x:v>4</x:v>
@@ -1451,7 +1472,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I6" s="4" t="s">
-        <x:v>177</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="J6" s="5"/>
       <x:c r="K6" s="5">
@@ -1463,19 +1484,19 @@
     </x:row>
     <x:row r="7" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A7" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="F7" s="6">
         <x:v>2</x:v>
@@ -1487,7 +1508,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I7" s="4" t="s">
-        <x:v>177</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="J7" s="5"/>
       <x:c r="K7" s="5">
@@ -1499,19 +1520,19 @@
     </x:row>
     <x:row r="8" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A8" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="F8" s="6">
         <x:v>3</x:v>
@@ -1523,7 +1544,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I8" s="4" t="s">
-        <x:v>177</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="J8" s="5"/>
       <x:c r="K8" s="5">
@@ -1535,19 +1556,19 @@
     </x:row>
     <x:row r="9" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A9" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>201</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>203</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="F9" s="6">
         <x:v>3</x:v>
@@ -1559,7 +1580,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I9" s="4" t="s">
-        <x:v>179</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J9" s="5"/>
       <x:c r="K9" s="5">
@@ -1571,34 +1592,34 @@
     </x:row>
     <x:row r="10" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A10" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="F10" s="8" t="s">
-        <x:v>41</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="G10" s="9" t="s">
-        <x:v>54</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="H10" s="3">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I10" s="4" t="s">
-        <x:v>179</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J10" s="5" t="s">
-        <x:v>27</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="K10" s="5">
         <x:v>37.349119163634199</x:v>
@@ -1609,19 +1630,19 @@
     </x:row>
     <x:row r="11" spans="1:12" ht="409.5">
       <x:c r="A11" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>193</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="F11" s="10">
         <x:v>0</x:v>
@@ -1633,10 +1654,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I11" s="4" t="s">
-        <x:v>179</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J11" s="12" t="s">
-        <x:v>110</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K11" s="5">
         <x:v>37.4068936118354</x:v>
@@ -1647,19 +1668,19 @@
     </x:row>
     <x:row r="12" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A12" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="F12" s="6">
         <x:v>2</x:v>
@@ -1671,10 +1692,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I12" s="4" t="s">
-        <x:v>177</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="J12" s="5" t="s">
-        <x:v>1</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="K12" s="5">
         <x:v>37.3868626447845</x:v>
@@ -1685,19 +1706,19 @@
     </x:row>
     <x:row r="13" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A13" s="1" t="s">
-        <x:v>161</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="F13" s="6">
         <x:v>4</x:v>
@@ -1709,7 +1730,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I13" s="4" t="s">
-        <x:v>177</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="J13" s="5"/>
       <x:c r="K13" s="5">
@@ -1721,19 +1742,19 @@
     </x:row>
     <x:row r="14" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A14" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>187</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F14" s="6">
         <x:v>1</x:v>
@@ -1745,7 +1766,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I14" s="4" t="s">
-        <x:v>179</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J14" s="5"/>
       <x:c r="K14" s="5">
@@ -1757,19 +1778,19 @@
     </x:row>
     <x:row r="15" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A15" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="F15" s="6">
         <x:v>3</x:v>
@@ -1781,7 +1802,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I15" s="4" t="s">
-        <x:v>177</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="J15" s="5"/>
       <x:c r="K15" s="5">
@@ -1793,19 +1814,19 @@
     </x:row>
     <x:row r="16" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A16" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="F16" s="6">
         <x:v>2</x:v>
@@ -1817,7 +1838,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I16" s="4" t="s">
-        <x:v>177</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="J16" s="5"/>
       <x:c r="K16" s="5">
@@ -1829,19 +1850,19 @@
     </x:row>
     <x:row r="17" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A17" s="1" t="s">
-        <x:v>166</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="F17" s="6">
         <x:v>3</x:v>
@@ -1853,7 +1874,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I17" s="4" t="s">
-        <x:v>177</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="J17" s="5"/>
       <x:c r="K17" s="5">
@@ -1865,19 +1886,19 @@
     </x:row>
     <x:row r="18" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A18" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="F18" s="6">
         <x:v>2</x:v>
@@ -1889,7 +1910,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I18" s="4" t="s">
-        <x:v>177</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="J18" s="5"/>
       <x:c r="K18" s="5">
@@ -1901,19 +1922,19 @@
     </x:row>
     <x:row r="19" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A19" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>158</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="F19" s="6">
         <x:v>2</x:v>
@@ -1922,10 +1943,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="H19" s="9" t="s">
-        <x:v>179</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I19" s="4" t="s">
-        <x:v>177</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="J19" s="5"/>
       <x:c r="K19" s="5">
@@ -1937,19 +1958,19 @@
     </x:row>
     <x:row r="20" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A20" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="F20" s="6">
         <x:v>1</x:v>
@@ -1961,7 +1982,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I20" s="4" t="s">
-        <x:v>179</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J20" s="5"/>
       <x:c r="K20" s="5">
@@ -1973,19 +1994,19 @@
     </x:row>
     <x:row r="21" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A21" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="F21" s="6">
         <x:v>2</x:v>
@@ -1997,7 +2018,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I21" s="4" t="s">
-        <x:v>177</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="J21" s="5"/>
       <x:c r="K21" s="5">
@@ -2009,34 +2030,34 @@
     </x:row>
     <x:row r="22" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A22" s="13" t="s">
-        <x:v>17</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B22" s="13" t="s">
-        <x:v>180</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C22" s="13" t="s">
-        <x:v>10</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D22" s="13" t="s">
-        <x:v>94</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E22" s="13" t="s">
-        <x:v>85</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="F22" s="14" t="s">
-        <x:v>57</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="G22" s="15" t="s">
-        <x:v>47</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="H22" s="3">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I22" s="4" t="s">
-        <x:v>177</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="J22" s="5" t="s">
-        <x:v>154</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="K22" s="5">
         <x:v>37.356151021147198</x:v>
@@ -2047,19 +2068,19 @@
     </x:row>
     <x:row r="23" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A23" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>185</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="F23" s="6">
         <x:v>2</x:v>
@@ -2071,7 +2092,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I23" s="4" t="s">
-        <x:v>177</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="J23" s="5"/>
       <x:c r="K23" s="5">
@@ -2083,19 +2104,19 @@
     </x:row>
     <x:row r="24" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A24" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="F24" s="6">
         <x:v>2</x:v>
@@ -2107,31 +2128,31 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="I24" s="4" t="s">
-        <x:v>177</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="J24" s="5"/>
       <x:c r="K24" s="20" t="s">
-        <x:v>0</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="L24" s="20" t="s">
-        <x:v>207</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A25" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="F25" s="6">
         <x:v>2</x:v>
@@ -2143,7 +2164,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I25" s="4" t="s">
-        <x:v>177</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="J25" s="5"/>
       <x:c r="K25" s="5">
@@ -2155,19 +2176,19 @@
     </x:row>
     <x:row r="26" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A26" s="1" t="s">
-        <x:v>156</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>150</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="F26" s="6">
         <x:v>2</x:v>
@@ -2179,7 +2200,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I26" s="4" t="s">
-        <x:v>177</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="J26" s="5"/>
       <x:c r="K26" s="5">
@@ -2191,19 +2212,19 @@
     </x:row>
     <x:row r="27" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A27" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="F27" s="6">
         <x:v>2</x:v>
@@ -2215,7 +2236,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I27" s="4" t="s">
-        <x:v>177</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="J27" s="5"/>
       <x:c r="K27" s="5">
@@ -2227,19 +2248,19 @@
     </x:row>
     <x:row r="28" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A28" s="1" t="s">
-        <x:v>167</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="F28" s="6">
         <x:v>3</x:v>
@@ -2251,7 +2272,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I28" s="4" t="s">
-        <x:v>177</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="J28" s="5"/>
       <x:c r="K28" s="5">
@@ -2263,19 +2284,19 @@
     </x:row>
     <x:row r="29" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A29" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B29" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C29" s="1" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D29" s="1" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E29" s="1" t="s">
         <x:v>164</x:v>
-      </x:c>
-      <x:c r="B29" s="1" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="C29" s="1" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D29" s="1" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="E29" s="1" t="s">
-        <x:v>80</x:v>
       </x:c>
       <x:c r="F29" s="6">
         <x:v>2</x:v>
@@ -2287,7 +2308,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I29" s="4" t="s">
-        <x:v>179</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J29" s="5"/>
       <x:c r="K29" s="5">
@@ -2299,19 +2320,19 @@
     </x:row>
     <x:row r="30" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A30" s="1" t="s">
-        <x:v>168</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="F30" s="6">
         <x:v>1</x:v>
@@ -2323,7 +2344,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I30" s="4" t="s">
-        <x:v>179</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J30" s="5"/>
       <x:c r="K30" s="5">
@@ -2335,19 +2356,19 @@
     </x:row>
     <x:row r="31" spans="1:12" ht="26.35000000000000142109">
       <x:c r="A31" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D31" s="16" t="s">
-        <x:v>202</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>190</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="F31" s="6">
         <x:v>3</x:v>
@@ -2359,7 +2380,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I31" s="4" t="s">
-        <x:v>179</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J31" s="5"/>
       <x:c r="K31" s="5">
@@ -2371,19 +2392,19 @@
     </x:row>
     <x:row r="32" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A32" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="F32" s="6">
         <x:v>2</x:v>
@@ -2395,7 +2416,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I32" s="4" t="s">
-        <x:v>179</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J32" s="5"/>
       <x:c r="K32" s="5">
@@ -2407,19 +2428,19 @@
     </x:row>
     <x:row r="33" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A33" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="F33" s="6">
         <x:v>2</x:v>
@@ -2431,7 +2452,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I33" s="4" t="s">
-        <x:v>177</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="J33" s="5"/>
       <x:c r="K33" s="5">
@@ -2443,19 +2464,19 @@
     </x:row>
     <x:row r="34" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A34" s="1" t="s">
-        <x:v>157</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F34" s="6">
         <x:v>3</x:v>
@@ -2467,7 +2488,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I34" s="4" t="s">
-        <x:v>179</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J34" s="5"/>
       <x:c r="K34" s="5">
@@ -2479,19 +2500,19 @@
     </x:row>
     <x:row r="35" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A35" s="1" t="s">
-        <x:v>162</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>189</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="F35" s="6">
         <x:v>2</x:v>
@@ -2503,7 +2524,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I35" s="4" t="s">
-        <x:v>177</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="J35" s="5"/>
       <x:c r="K35" s="5">
@@ -2515,19 +2536,19 @@
     </x:row>
     <x:row r="36" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A36" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="F36" s="6">
         <x:v>3</x:v>
@@ -2539,31 +2560,31 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I36" s="4" t="s">
-        <x:v>177</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="J36" s="5"/>
-      <x:c r="K36" s="20" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="L36" s="20" t="s">
-        <x:v>6</x:v>
+      <x:c r="K36" s="20">
+        <x:v>37.3519773034689</x:v>
+      </x:c>
+      <x:c r="L36" s="20">
+        <x:v>126.732086373375</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A37" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="F37" s="6">
         <x:v>2</x:v>
@@ -2575,7 +2596,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I37" s="4" t="s">
-        <x:v>179</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J37" s="5"/>
       <x:c r="K37" s="5">
@@ -2587,19 +2608,19 @@
     </x:row>
     <x:row r="38" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A38" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="F38" s="6">
         <x:v>2</x:v>
@@ -2611,10 +2632,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I38" s="4" t="s">
-        <x:v>177</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="J38" s="5" t="s">
-        <x:v>111</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="K38" s="5">
         <x:v>37.387563889027803</x:v>
@@ -2625,19 +2646,19 @@
     </x:row>
     <x:row r="39" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A39" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>196</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="F39" s="6">
         <x:v>2</x:v>
@@ -2649,7 +2670,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I39" s="4" t="s">
-        <x:v>177</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="J39" s="5"/>
       <x:c r="K39" s="5">
@@ -2661,19 +2682,19 @@
     </x:row>
     <x:row r="40" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A40" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>158</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="F40" s="6">
         <x:v>2</x:v>
@@ -2685,7 +2706,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="I40" s="4" t="s">
-        <x:v>177</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="J40" s="5"/>
       <x:c r="K40" s="5">
@@ -2697,19 +2718,19 @@
     </x:row>
     <x:row r="41" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A41" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="F41" s="6">
         <x:v>2</x:v>
@@ -2721,7 +2742,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I41" s="4" t="s">
-        <x:v>177</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="J41" s="5"/>
       <x:c r="K41" s="5">
@@ -2733,19 +2754,19 @@
     </x:row>
     <x:row r="42" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A42" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C42" s="1" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D42" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E42" s="1" t="s">
         <x:v>180</x:v>
-      </x:c>
-      <x:c r="C42" s="1" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="D42" s="1" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="E42" s="1" t="s">
-        <x:v>74</x:v>
       </x:c>
       <x:c r="F42" s="6">
         <x:v>2</x:v>
@@ -2757,7 +2778,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I42" s="4" t="s">
-        <x:v>177</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="J42" s="5"/>
       <x:c r="K42" s="5">
@@ -2769,34 +2790,34 @@
     </x:row>
     <x:row r="43" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A43" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>147</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>197</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="F43" s="17" t="s">
-        <x:v>57</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="G43" s="15" t="s">
-        <x:v>8</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H43" s="3">
         <x:v>3</x:v>
       </x:c>
       <x:c r="I43" s="4" t="s">
-        <x:v>177</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="J43" s="5" t="s">
-        <x:v>154</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="K43" s="5">
         <x:v>37.447733087317197</x:v>
@@ -2807,19 +2828,19 @@
     </x:row>
     <x:row r="44" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A44" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="F44" s="6">
         <x:v>3</x:v>
@@ -2831,7 +2852,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I44" s="4" t="s">
-        <x:v>177</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="J44" s="5"/>
       <x:c r="K44" s="5">
@@ -2843,19 +2864,19 @@
     </x:row>
     <x:row r="45" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A45" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>149</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>200</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="F45" s="6">
         <x:v>3</x:v>
@@ -2867,7 +2888,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I45" s="4" t="s">
-        <x:v>177</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="J45" s="5"/>
       <x:c r="K45" s="5">
@@ -2879,34 +2900,34 @@
     </x:row>
     <x:row r="46" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A46" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>188</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="F46" s="17" t="s">
-        <x:v>57</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="G46" s="15" t="s">
-        <x:v>38</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="H46" s="3">
         <x:v>3</x:v>
       </x:c>
       <x:c r="I46" s="4" t="s">
-        <x:v>177</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="J46" s="5" t="s">
-        <x:v>154</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="K46" s="5">
         <x:v>37.3410220277447</x:v>
@@ -2917,19 +2938,19 @@
     </x:row>
     <x:row r="47" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A47" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>158</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="F47" s="6">
         <x:v>2</x:v>
@@ -2941,7 +2962,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I47" s="4" t="s">
-        <x:v>177</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="J47" s="5"/>
       <x:c r="K47" s="5">
@@ -2953,19 +2974,19 @@
     </x:row>
     <x:row r="48" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A48" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>186</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="F48" s="6">
         <x:v>3</x:v>
@@ -2977,7 +2998,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="I48" s="4" t="s">
-        <x:v>177</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="J48" s="5"/>
       <x:c r="K48" s="5">
@@ -2989,19 +3010,19 @@
     </x:row>
     <x:row r="49" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A49" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>179</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="F49" s="7">
         <x:v>0</x:v>
@@ -3013,10 +3034,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I49" s="4" t="s">
-        <x:v>179</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J49" s="5" t="s">
-        <x:v>119</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="K49" s="5">
         <x:v>37.4360625257819</x:v>
@@ -3027,19 +3048,19 @@
     </x:row>
     <x:row r="50" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A50" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>169</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>173</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="F50" s="6">
         <x:v>1</x:v>
@@ -3051,7 +3072,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I50" s="4" t="s">
-        <x:v>179</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J50" s="5"/>
       <x:c r="K50" s="5">
@@ -3063,19 +3084,19 @@
     </x:row>
     <x:row r="51" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A51" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="F51" s="6">
         <x:v>3</x:v>
@@ -3087,7 +3108,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I51" s="4" t="s">
-        <x:v>177</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="J51" s="5"/>
       <x:c r="K51" s="5">
@@ -3099,34 +3120,34 @@
     </x:row>
     <x:row r="52" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A52" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>198</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>199</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="F52" s="18" t="s">
-        <x:v>73</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="G52" s="19" t="s">
-        <x:v>48</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="H52" s="3">
         <x:v>2</x:v>
       </x:c>
       <x:c r="I52" s="4" t="s">
-        <x:v>177</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="J52" s="5" t="s">
-        <x:v>69</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="K52" s="5">
         <x:v>37.365614337187303</x:v>
@@ -3137,19 +3158,19 @@
     </x:row>
     <x:row r="53" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A53" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>206</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>191</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="F53" s="6">
         <x:v>1</x:v>
@@ -3161,7 +3182,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I53" s="4" t="s">
-        <x:v>179</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J53" s="5"/>
       <x:c r="K53" s="5">

--- a/data/elementary.xlsx
+++ b/data/elementary.xlsx
@@ -19,36 +19,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="206">
-  <x:si>
-    <x:t>위도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경도</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 주소</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 비고</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공립</x:t>
-  </x:si>
-  <x:si>
-    <x:t>계수초등학교 학구 중 계수동은 부천시 소사옥길중학군과 공동학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 능곡중앙로 22</x:t>
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="208">
+  <x:si>
+    <x:t>⊙연성초등학교 학구 중 목감동 1~2통, 3통 4반~6반은 목감중학구 및 안산시 안산중학구와 공동학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-1108</x:t>
   </x:si>
   <x:si>
     <x:t>⊙도창초등학교 학구 중 매화동 5통, 매화동 20~22통은 시흥매화중학구와 공동학구
@@ -56,590 +32,620 @@
 ⊙도창초등학교 학구 중 과림동 1통(노무저리 제외),  과림동 2통은 광명시 광명중학군과 공동학구</x:t>
   </x:si>
   <x:si>
-    <x:t>⊙연성초등학교 학구 중 목감동 1~2통, 3통 4반~6반은 목감중학구 및 안산시 안산중학구와 공동학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧라라초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧누리초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥매화초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한국글로벌중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥능곡초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥은행초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥장현초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧라온초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥신일초등학교</x:t>
+    <x:t xml:space="preserve"> 주소</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 비고</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-365-8003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7014-4072</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-363-3003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-364-1700</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8040-6505</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-412-4300</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-312-3600</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-0204</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7096-6872</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8099-9703</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-2576</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-503-0560</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 은행고길 18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-364-7903</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 나분들길 44</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-4648-5770</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7014-8703</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7016-3005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥가온초등학교</x:t>
   </x:si>
   <x:si>
     <x:t>군서미래국제학교(초)</x:t>
   </x:si>
   <x:si>
-    <x:t>목감중학구/조남중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수/순회/일반)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧해솔초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시화나래초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥월곶초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소래중학구/연성중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 특수/순회학급수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧한울초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥가온초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보조인력 배치 유/무</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥도원초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>126.730065</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 월곶중앙로 18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 배곧 4로 44-5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 월곶해안로 69</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 장현능곡로 33</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 군자로465번길 7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 목감남서로 68</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 큰솔로 7번길 10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 서울대학로 255</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 목감둘레로 229-9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 죽율로 45-42</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 중심상가로 257</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 서울대학로 150-17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 정왕대로 143번길 15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 해송십리로 472-30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 수인로 3413번길 34</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 옥구천동로 433-25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 신현로 202번길 31</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 정왕천로427번길 30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 대은로 104번길 29-10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 수인로3247번길 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 정왕대로118번길 27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 하중로 209번길 10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 정왕대로 53번길 14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정왕초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>목감중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정왕중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 연락처</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 학교설립별</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 학교명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>군자중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16/ 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>군자초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>검바위초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>승지초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장곡중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소래초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>서해초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>산현초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>군서초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>웃터골초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>진영초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>함현초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>목감초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>포리초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>신천초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도일초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>조남초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥매화중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>은빛초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시화중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시화초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하중초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소래중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수/순회)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥능곡중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연성중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>진말초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연성초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2/ 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대야초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21/ 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>월곶중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>월포초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>서촌초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>생금초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장곡초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도창초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥터초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>은계초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>냉정초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24/ 12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9/ 3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>금모래초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3학기제</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3/ 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16/ 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>계수초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>운흥초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>송운초등학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>⊙목감초등학교 학구 중 목감동 4통, 6통은 안산중학구와 공동학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>37.360228</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 배곧1로 28-25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 대은로103번길 24</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7096-7772</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-365-8003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한국글로벌중학구/ 소래중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 계수로 203</x:t>
-  </x:si>
-  <x:si>
-    <x:t>특수/순회학급 배치 학생 수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일반학급 배치 학생 수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-310-4695</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7096-7801</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8042-0004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-503-0560</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-494-4167</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-1303</x:t>
-  </x:si>
-  <x:si>
     <x:t>경기도 시흥시 능곡군자로 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7096-6083</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7015-4404</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 매화1로 6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-2302</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 대골안길 31</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-0802</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7016-3005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 역전로 455</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-503-1020</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-0204</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-1683</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7014-4072</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-364-3410</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 승지로 110</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(복합특수/시간제/일반)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8099-9703</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-364-7903</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-2576</x:t>
-  </x:si>
-  <x:si>
-    <x:t>복특 6학급/ 시간제 2학급</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-312-3600</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-2915</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 나분들길 44</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-2204</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8099-5900</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-1108</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8063-7873</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-0603</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-434-6152</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-363-5904</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-363-3003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8032-6504</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7096-6872</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-500-0601</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8042-2502</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 포도원로 88</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-364-1700</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7096-7706</x:t>
   </x:si>
   <x:si>
     <x:t>한국글로벌중학구
 /소래중학구</x:t>
   </x:si>
   <x:si>
-    <x:t>070-4648-5770</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7014-8703</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-412-4300</x:t>
+    <x:t>070-7097-1553</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8042-0004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-1683</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 포도원로 39</x:t>
+  </x:si>
+  <x:si>
+    <x:t>성인 · 주부 · 어르신</x:t>
+  </x:si>
+  <x:si>
+    <x:t>복특 6학급/ 시간제 2학급</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한여울초등학교(복합특수)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-503-1538</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-317-2701</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8042-0700</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 계수로 203</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-4878-2804</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7096-7801</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 군자로 539</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8063-2903</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-2915</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-2707</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7096-6083</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-0603</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8042-2502</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8063-7873</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 포도원로 88</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-494-4167</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-364-3410</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8099-5900</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-2302</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7096-7706</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-490-8204</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8032-6504</x:t>
   </x:si>
   <x:si>
     <x:t>031-8044-1261</x:t>
   </x:si>
   <x:si>
-    <x:t>070-7097-1553</x:t>
-  </x:si>
-  <x:si>
-    <x:t>성인 · 주부 · 어르신</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 은행고길 18</x:t>
+    <x:t>031-363-5904</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 옥터로 33</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 역전로 369</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-0802</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(복합특수/시간제/일반)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-2204</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 역전로 455</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-1303</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-500-0601</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7015-4404</x:t>
   </x:si>
   <x:si>
     <x:t>031-363-1526</x:t>
   </x:si>
   <x:si>
-    <x:t>경기도 시흥시 군자로 539</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-2707</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8063-2903</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-4878-2804</x:t>
+    <x:t>경기도 시흥시 매화1로 6</x:t>
   </x:si>
   <x:si>
     <x:t>031-8085-7004</x:t>
   </x:si>
   <x:si>
-    <x:t>031-8042-0700</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8040-6505</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한여울초등학교(복합특수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-490-8204</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 포도원로 39</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 역전로 369</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 옥터로 33</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-503-1538</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-317-2701</x:t>
+    <x:t>031-434-6152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한국글로벌중학구/ 소래중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 승지로 110</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 대골안길 31</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-310-4695</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7096-7772</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-503-1020</x:t>
+  </x:si>
+  <x:si>
+    <x:t>계수초등학교 학구 중 계수동은 부천시 소사옥길중학군과 공동학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21/ 3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>웃터골초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하중초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>승지초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16/ 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장곡초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군자초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24/ 12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16/ 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소래초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정왕초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대야초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>은빛초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연성초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>검바위초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>송운초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도창초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>함현초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>냉정초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군서초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>진영초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신천초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도일초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>금모래초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥터초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>조남초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서촌초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>포리초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>목감초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>월포초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>계수초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3학기제</x:t>
+  </x:si>
+  <x:si>
+    <x:t>운흥초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥매화중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3/ 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서해초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시화중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군자중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>목감중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정왕중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>산현초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소래중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>진말초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>은계초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장곡중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>126.72</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연성중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>생금초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2/ 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥능곡중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>월곶중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>37.34</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수/순회)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9/ 3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시화초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수/순회/일반)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한국글로벌중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧누리초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧라라초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧해솔초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시화나래초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>목감중학구/조남중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소래중학구/연성중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>126.730065</x:t>
+  </x:si>
+  <x:si>
+    <x:t>37.360228,</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 죽율로 45-42</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 능곡중앙로 22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 서울대학로 255</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 수인로2793번길 6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 황고개로 567</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 배곧4로 94-39</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 목감남서로 68</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 장곡로 70번길 12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 목감둘레로 109</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 시청로80번길 5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 월곶해안로 69</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 대은로 16-29</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 거북섬남로 70</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 중심상가로 257</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 군자로465번길 7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 대은로103번길 24</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">경기도 시흥시 은행동 663 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 호현로 27번길 14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 큰솔로 7번길 10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 배곧 4로 44-5</x:t>
   </x:si>
   <x:si>
     <x:t>경기도 시흥시 목감초등길 49</x:t>
   </x:si>
   <x:si>
-    <x:t>경기도 시흥시 대은로 16-29</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 배곧4로 94-39</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 거북섬남로 70</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 장곡로 70번길 12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 황고개로 567</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 호현로 27번길 14</x:t>
+    <x:t>경기도 시흥시 군서마을로 101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 장현능곡로 33</x:t>
   </x:si>
   <x:si>
     <x:t>경기도 시흥시 신천로 7번길 12</x:t>
   </x:si>
   <x:si>
-    <x:t>경기도 시흥시 시청로80번길 5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 군서마을로 101</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 목감둘레로 109</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 수인로2793번길 6</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">경기도 시흥시 은행동 663 </x:t>
+    <x:t>경기도 시흥시 배곧1로 28-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 월곶중앙로 18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 목감둘레로 229-9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>⊙목감초등학교 학구 중 목감동 4통, 6통은 안산중학구와 공동학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 옥구천동로 433-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 정왕대로 53번길 14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 수인로 3413번길 34</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 수인로3247번길 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 정왕대로118번길 27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 신현로 202번길 31</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 하중로 209번길 10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 정왕천로427번길 30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 서울대학로 150-17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 해송십리로 472-30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 대은로 104번길 29-10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 정왕대로 143번길 15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공립</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>위도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥은행초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥매화초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥도원초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧라온초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥능곡초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥신일초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥월곶초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧한울초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥장현초등학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일반학급 배치 학생 수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>특수/순회학급 배치 학생 수</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 학교명</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 연락처</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 학교설립별</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 특수/순회학급수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보조인력 배치 유/무</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1264,57 +1270,57 @@
   <x:sheetData>
     <x:row r="1" spans="1:12">
       <x:c r="A1" t="s">
-        <x:v>62</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="B1" t="s">
-        <x:v>61</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="C1" t="s">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D1" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="E1" t="s">
-        <x:v>60</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="F1" t="s">
-        <x:v>28</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="G1" t="s">
-        <x:v>124</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="H1" t="s">
-        <x:v>125</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="I1" t="s">
-        <x:v>31</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="J1" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="K1" t="s">
-        <x:v>0</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="L1" t="s">
-        <x:v>1</x:v>
+        <x:v>190</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A2" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>170</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>191</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F2" s="2">
         <x:v>3</x:v>
@@ -1326,7 +1332,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I2" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="J2" s="5"/>
       <x:c r="K2" s="5">
@@ -1338,19 +1344,19 @@
     </x:row>
     <x:row r="3" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A3" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>174</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F3" s="6">
         <x:v>1</x:v>
@@ -1362,10 +1368,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I3" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="J3" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="K3" s="5">
         <x:v>37.453471946211501</x:v>
@@ -1376,19 +1382,19 @@
     </x:row>
     <x:row r="4" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A4" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>202</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>178</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F4" s="7">
         <x:v>0</x:v>
@@ -1400,7 +1406,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I4" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="J4" s="5"/>
       <x:c r="K4" s="5">
@@ -1412,19 +1418,19 @@
     </x:row>
     <x:row r="5" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A5" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>166</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F5" s="6">
         <x:v>3</x:v>
@@ -1436,7 +1442,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I5" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="J5" s="5"/>
       <x:c r="K5" s="5">
@@ -1448,31 +1454,31 @@
     </x:row>
     <x:row r="6" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A6" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>179</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>171</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F6" s="6">
         <x:v>4</x:v>
       </x:c>
       <x:c r="G6" s="3">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H6" s="3">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I6" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="J6" s="5"/>
       <x:c r="K6" s="5">
@@ -1484,19 +1490,19 @@
     </x:row>
     <x:row r="7" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A7" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>170</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F7" s="6">
         <x:v>2</x:v>
@@ -1508,7 +1514,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I7" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="J7" s="5"/>
       <x:c r="K7" s="5">
@@ -1520,19 +1526,19 @@
     </x:row>
     <x:row r="8" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A8" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>189</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>184</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F8" s="6">
         <x:v>3</x:v>
@@ -1544,7 +1550,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I8" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="J8" s="5"/>
       <x:c r="K8" s="5">
@@ -1556,31 +1562,31 @@
     </x:row>
     <x:row r="9" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A9" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>162</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F9" s="6">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G9" s="3">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H9" s="3">
         <x:v>2</x:v>
       </x:c>
       <x:c r="I9" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="J9" s="5"/>
       <x:c r="K9" s="5">
@@ -1592,34 +1598,34 @@
     </x:row>
     <x:row r="10" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A10" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F10" s="8" t="s">
-        <x:v>94</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="G10" s="9" t="s">
-        <x:v>108</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="H10" s="3">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I10" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="J10" s="5" t="s">
-        <x:v>88</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="K10" s="5">
         <x:v>37.349119163634199</x:v>
@@ -1630,19 +1636,19 @@
     </x:row>
     <x:row r="11" spans="1:12" ht="409.5">
       <x:c r="A11" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>170</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>204</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F11" s="10">
         <x:v>0</x:v>
@@ -1654,10 +1660,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I11" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="J11" s="12" t="s">
-        <x:v>10</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K11" s="5">
         <x:v>37.4068936118354</x:v>
@@ -1668,19 +1674,19 @@
     </x:row>
     <x:row r="12" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A12" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>193</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F12" s="6">
         <x:v>2</x:v>
@@ -1692,10 +1698,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I12" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="J12" s="5" t="s">
-        <x:v>116</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="K12" s="5">
         <x:v>37.3868626447845</x:v>
@@ -1706,31 +1712,31 @@
     </x:row>
     <x:row r="13" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A13" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>181</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F13" s="6">
         <x:v>4</x:v>
       </x:c>
       <x:c r="G13" s="3">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H13" s="3">
         <x:v>5</x:v>
       </x:c>
       <x:c r="I13" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="J13" s="5"/>
       <x:c r="K13" s="5">
@@ -1742,19 +1748,19 @@
     </x:row>
     <x:row r="14" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F14" s="6">
         <x:v>1</x:v>
@@ -1766,7 +1772,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I14" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="J14" s="5"/>
       <x:c r="K14" s="5">
@@ -1778,19 +1784,19 @@
     </x:row>
     <x:row r="15" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A15" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>163</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F15" s="6">
         <x:v>3</x:v>
@@ -1802,7 +1808,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I15" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="J15" s="5"/>
       <x:c r="K15" s="5">
@@ -1814,19 +1820,19 @@
     </x:row>
     <x:row r="16" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A16" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>148</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F16" s="6">
         <x:v>2</x:v>
@@ -1838,7 +1844,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I16" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="J16" s="5"/>
       <x:c r="K16" s="5">
@@ -1850,19 +1856,19 @@
     </x:row>
     <x:row r="17" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A17" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>173</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F17" s="6">
         <x:v>3</x:v>
@@ -1874,7 +1880,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I17" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="J17" s="5"/>
       <x:c r="K17" s="5">
@@ -1886,19 +1892,19 @@
     </x:row>
     <x:row r="18" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A18" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>158</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F18" s="6">
         <x:v>2</x:v>
@@ -1910,7 +1916,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I18" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="J18" s="5"/>
       <x:c r="K18" s="5">
@@ -1922,19 +1928,19 @@
     </x:row>
     <x:row r="19" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A19" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>185</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F19" s="6">
         <x:v>2</x:v>
@@ -1943,10 +1949,10 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="H19" s="9" t="s">
-        <x:v>4</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="I19" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="J19" s="5"/>
       <x:c r="K19" s="5">
@@ -1958,19 +1964,19 @@
     </x:row>
     <x:row r="20" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A20" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F20" s="6">
         <x:v>1</x:v>
@@ -1982,7 +1988,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I20" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="J20" s="5"/>
       <x:c r="K20" s="5">
@@ -1994,19 +2000,19 @@
     </x:row>
     <x:row r="21" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A21" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="C21" s="1" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="D21" s="1" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="E21" s="1" t="s">
         <x:v>7</x:v>
-      </x:c>
-      <x:c r="C21" s="1" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="D21" s="1" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E21" s="1" t="s">
-        <x:v>144</x:v>
       </x:c>
       <x:c r="F21" s="6">
         <x:v>2</x:v>
@@ -2018,7 +2024,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I21" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="J21" s="5"/>
       <x:c r="K21" s="5">
@@ -2030,34 +2036,34 @@
     </x:row>
     <x:row r="22" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A22" s="13" t="s">
-        <x:v>70</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B22" s="13" t="s">
-        <x:v>7</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C22" s="13" t="s">
-        <x:v>59</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D22" s="13" t="s">
-        <x:v>56</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="E22" s="13" t="s">
-        <x:v>160</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F22" s="14" t="s">
-        <x:v>111</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="G22" s="15" t="s">
-        <x:v>112</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="H22" s="3">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I22" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="J22" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="K22" s="5">
         <x:v>37.356151021147198</x:v>
@@ -2068,31 +2074,31 @@
     </x:row>
     <x:row r="23" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A23" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>199</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F23" s="6">
         <x:v>2</x:v>
       </x:c>
       <x:c r="G23" s="3">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="H23" s="3">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I23" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="J23" s="5"/>
       <x:c r="K23" s="5">
@@ -2104,19 +2110,19 @@
     </x:row>
     <x:row r="24" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A24" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F24" s="6">
         <x:v>2</x:v>
@@ -2128,31 +2134,31 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="I24" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="J24" s="5"/>
       <x:c r="K24" s="20" t="s">
-        <x:v>117</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="L24" s="20" t="s">
-        <x:v>33</x:v>
+        <x:v>145</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A25" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>156</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F25" s="6">
         <x:v>2</x:v>
@@ -2164,7 +2170,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I25" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="J25" s="5"/>
       <x:c r="K25" s="5">
@@ -2176,31 +2182,31 @@
     </x:row>
     <x:row r="26" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A26" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>196</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F26" s="6">
         <x:v>2</x:v>
       </x:c>
       <x:c r="G26" s="3">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H26" s="3">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I26" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="J26" s="5"/>
       <x:c r="K26" s="5">
@@ -2212,19 +2218,19 @@
     </x:row>
     <x:row r="27" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A27" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F27" s="6">
         <x:v>2</x:v>
@@ -2236,7 +2242,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I27" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="J27" s="5"/>
       <x:c r="K27" s="5">
@@ -2248,19 +2254,19 @@
     </x:row>
     <x:row r="28" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A28" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>168</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F28" s="6">
         <x:v>3</x:v>
@@ -2272,7 +2278,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I28" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="J28" s="5"/>
       <x:c r="K28" s="5">
@@ -2284,19 +2290,19 @@
     </x:row>
     <x:row r="29" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A29" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>164</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F29" s="6">
         <x:v>2</x:v>
@@ -2308,7 +2314,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I29" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="J29" s="5"/>
       <x:c r="K29" s="5">
@@ -2320,19 +2326,19 @@
     </x:row>
     <x:row r="30" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A30" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>157</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F30" s="6">
         <x:v>1</x:v>
@@ -2344,7 +2350,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I30" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="J30" s="5"/>
       <x:c r="K30" s="5">
@@ -2356,19 +2362,19 @@
     </x:row>
     <x:row r="31" spans="1:12" ht="26.35000000000000142109">
       <x:c r="A31" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D31" s="16" t="s">
-        <x:v>135</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F31" s="6">
         <x:v>3</x:v>
@@ -2380,7 +2386,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I31" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="J31" s="5"/>
       <x:c r="K31" s="5">
@@ -2392,19 +2398,19 @@
     </x:row>
     <x:row r="32" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A32" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>200</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>182</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F32" s="6">
         <x:v>2</x:v>
@@ -2416,7 +2422,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I32" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="J32" s="5"/>
       <x:c r="K32" s="5">
@@ -2428,19 +2434,19 @@
     </x:row>
     <x:row r="33" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A33" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>149</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F33" s="6">
         <x:v>2</x:v>
@@ -2452,7 +2458,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I33" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="J33" s="5"/>
       <x:c r="K33" s="5">
@@ -2464,19 +2470,19 @@
     </x:row>
     <x:row r="34" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A34" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>170</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F34" s="6">
         <x:v>3</x:v>
@@ -2488,7 +2494,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I34" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="J34" s="5"/>
       <x:c r="K34" s="5">
@@ -2500,19 +2506,19 @@
     </x:row>
     <x:row r="35" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A35" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>201</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="F35" s="6">
         <x:v>2</x:v>
@@ -2524,7 +2530,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I35" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="J35" s="5"/>
       <x:c r="K35" s="5">
@@ -2536,19 +2542,19 @@
     </x:row>
     <x:row r="36" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A36" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F36" s="6">
         <x:v>3</x:v>
@@ -2560,43 +2566,43 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I36" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="J36" s="5"/>
-      <x:c r="K36" s="20">
-        <x:v>37.3519773034689</x:v>
-      </x:c>
-      <x:c r="L36" s="20">
-        <x:v>126.732086373375</x:v>
+      <x:c r="K36" s="20" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="L36" s="20" t="s">
+        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A37" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>167</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F37" s="6">
         <x:v>2</x:v>
       </x:c>
       <x:c r="G37" s="3">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H37" s="3">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I37" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="J37" s="5"/>
       <x:c r="K37" s="5">
@@ -2611,16 +2617,16 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F38" s="6">
         <x:v>2</x:v>
@@ -2632,10 +2638,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I38" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="J38" s="5" t="s">
-        <x:v>11</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K38" s="5">
         <x:v>37.387563889027803</x:v>
@@ -2646,19 +2652,19 @@
     </x:row>
     <x:row r="39" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A39" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="D39" s="1" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="D39" s="1" t="s">
-        <x:v>190</x:v>
-      </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F39" s="6">
         <x:v>2</x:v>
@@ -2670,7 +2676,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I39" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="J39" s="5"/>
       <x:c r="K39" s="5">
@@ -2682,31 +2688,31 @@
     </x:row>
     <x:row r="40" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A40" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>203</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>161</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F40" s="6">
         <x:v>2</x:v>
       </x:c>
       <x:c r="G40" s="3">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H40" s="3">
         <x:v>10</x:v>
       </x:c>
       <x:c r="I40" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="J40" s="5"/>
       <x:c r="K40" s="5">
@@ -2718,19 +2724,19 @@
     </x:row>
     <x:row r="41" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A41" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>170</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>169</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F41" s="6">
         <x:v>2</x:v>
@@ -2742,7 +2748,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I41" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="J41" s="5"/>
       <x:c r="K41" s="5">
@@ -2754,19 +2760,19 @@
     </x:row>
     <x:row r="42" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A42" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F42" s="6">
         <x:v>2</x:v>
@@ -2778,7 +2784,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I42" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="J42" s="5"/>
       <x:c r="K42" s="5">
@@ -2790,34 +2796,34 @@
     </x:row>
     <x:row r="43" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A43" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>170</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="F43" s="17" t="s">
-        <x:v>111</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="G43" s="15" t="s">
-        <x:v>64</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="H43" s="3">
         <x:v>3</x:v>
       </x:c>
       <x:c r="I43" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="J43" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="K43" s="5">
         <x:v>37.447733087317197</x:v>
@@ -2828,19 +2834,19 @@
     </x:row>
     <x:row r="44" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A44" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>170</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>183</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F44" s="6">
         <x:v>3</x:v>
@@ -2852,7 +2858,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I44" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="J44" s="5"/>
       <x:c r="K44" s="5">
@@ -2864,19 +2870,19 @@
     </x:row>
     <x:row r="45" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A45" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>197</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F45" s="6">
         <x:v>3</x:v>
@@ -2888,7 +2894,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I45" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="J45" s="5"/>
       <x:c r="K45" s="5">
@@ -2900,34 +2906,34 @@
     </x:row>
     <x:row r="46" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A46" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F46" s="17" t="s">
-        <x:v>111</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="G46" s="15" t="s">
-        <x:v>96</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="H46" s="3">
         <x:v>3</x:v>
       </x:c>
       <x:c r="I46" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="J46" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="K46" s="5">
         <x:v>37.3410220277447</x:v>
@@ -2938,19 +2944,19 @@
     </x:row>
     <x:row r="47" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A47" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>187</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F47" s="6">
         <x:v>2</x:v>
@@ -2962,7 +2968,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I47" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="J47" s="5"/>
       <x:c r="K47" s="5">
@@ -2974,19 +2980,19 @@
     </x:row>
     <x:row r="48" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A48" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>198</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F48" s="6">
         <x:v>3</x:v>
@@ -2998,7 +3004,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="I48" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="J48" s="5"/>
       <x:c r="K48" s="5">
@@ -3010,19 +3016,19 @@
     </x:row>
     <x:row r="49" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A49" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>188</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F49" s="7">
         <x:v>0</x:v>
@@ -3034,10 +3040,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I49" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="J49" s="5" t="s">
-        <x:v>176</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="K49" s="5">
         <x:v>37.4360625257819</x:v>
@@ -3048,19 +3054,19 @@
     </x:row>
     <x:row r="50" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A50" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>150</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F50" s="6">
         <x:v>1</x:v>
@@ -3072,7 +3078,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I50" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="J50" s="5"/>
       <x:c r="K50" s="5">
@@ -3084,19 +3090,19 @@
     </x:row>
     <x:row r="51" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A51" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F51" s="6">
         <x:v>3</x:v>
@@ -3108,7 +3114,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I51" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="J51" s="5"/>
       <x:c r="K51" s="5">
@@ -3120,34 +3126,34 @@
     </x:row>
     <x:row r="52" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A52" s="1" t="s">
-        <x:v>186</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F52" s="18" t="s">
-        <x:v>151</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G52" s="19" t="s">
-        <x:v>107</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H52" s="3">
         <x:v>2</x:v>
       </x:c>
       <x:c r="I52" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="J52" s="5" t="s">
-        <x:v>147</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="K52" s="5">
         <x:v>37.365614337187303</x:v>
@@ -3158,19 +3164,19 @@
     </x:row>
     <x:row r="53" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A53" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F53" s="6">
         <x:v>1</x:v>
@@ -3182,7 +3188,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I53" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="J53" s="5"/>
       <x:c r="K53" s="5">
